--- a/Community & Equity Dimensions of Mobility Literature Review.review.xlsx
+++ b/Community & Equity Dimensions of Mobility Literature Review.review.xlsx
@@ -142,70 +142,34 @@
     <author>lit-review-verifier</author>
   </authors>
   <commentList>
-    <comment ref="G3" authorId="0" shapeId="0">
+    <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>Original: Disabled transit riders in Austin and Seattle face similar first and last mile barriers despite different transit systems and geographies, shaped by intersectionality, built environment quality, social context, and relationships with agencies. Disabled voices are systematically excluded from planning, perpetuating inequitable outcomes.
-Why: The original listed only four of the five factors the author names on p. 2 ('intersectionality, social context, built environment quality, confidence, and relationships with public agencies'). Confidence was omitted, and it is the factor that speaks to relational trust, one of our three community values: a rider describes not feeling confident enough to ask an operator to lower the bus (p. 4).</t>
+        <t>Original: Secondary comparative analysis, not the authors' own fieldwork, of five California Clean Mobility Options community transportation needs assessment awardees' final reports and survey data, benchmarked against long range transportation plans' public participation records. Awardees used varied methods: surveys, workshops, focus groups, interviews, community meetings, stakeholder phone calls, photovoice, collaborative mapping, and one virtual reality component, often co hosted with community based organizations. The authors evaluate whether these funded, explicitly inclusive processes reached and empowered underrepresented residents, not whether their own study did.
+Why: Unsupported number: the cell says 'five' awardees, but the paper states 'The 24 awardees' and 'After analyzing the contents of all 24 needs assessment final reports'. The study covered all 24, not five. Only the count is changed; the rest of the description is accurate.</t>
       </text>
     </comment>
-    <comment ref="K3" authorId="0" shapeId="0">
+    <comment ref="O9" authorId="0" shapeId="0">
       <text>
-        <t>Original: Supports both halves of the claim. Mobility access is unevenly distributed by disability type, gender, and race even in cities with strong accessibility investment, and infrastructure built to minimum ADA standards without disabled riders' participation reproduces exclusion along the first and last mile.
-Why: The original asserted exclusion from participation but cited no evidence for it. P. 6 supplies the paper's most directly load-bearing material for this section's participation half: 'disabled travelers are seldom in the room when transportation decisions are made' and a participant on the engagement process, 'Something that was frustrating the whole time was how white and male-dominated [the process was].' Adding it grounds the claim in the paper's own findings.</t>
+        <t>Original: The authors' own method is 28 semi-structured interviews with BIPOC transportation professionals, conducted between April 2020 and 2021, recruited through referrals and thematically coded, asking how they view equity work in their agencies. Interviewees describe two contrasting community engagement models: performative outreach that checklists community input after decisions are already made, versus a Central Valley group's monthly equity led agenda meetings, where residents envision the community they want, that vision is translated into plans and policies, and organizers then advocate to get those plans implemented so residents benefit from their own feedback.
+Why: Date error: the cell says interviews were 'conducted between April 2020 and 2021'. The paper states 'recruitment and interviews occurred between April and August 2020' and 'Interviews were conducted in two rounds'. There was no 2021 interview wave; the only April 2021 date in the PDF is a citation access date. Corrected to April to August 2020, two rounds.</t>
       </text>
     </comment>
-    <comment ref="M13" authorId="0" shapeId="0">
+    <comment ref="O20" authorId="0" shapeId="0">
       <text>
-        <t>Original: "excluding some from participating bequeaths unequal powers among stakeholders" (p. 14).
-Why: Citation integrity: on p. 14 this sentence is not the authors' own wording, it is a quotation they take from Al-Sharari (2022, p. 1316). As originally written the row would attribute another scholar's words to McCullogh et al. The quote is accurate and stays, but the nested source is now named.</t>
+        <t>Original: Case study of a Berlin Pankow Kiezblock traffic calming initiative, analyzed by the authors through participation reports, focus group transcripts, and workshop documentation from a co-production process, not the authors' own fieldwork with residents. A civic initiative had already drafted 19 conceptual layouts before formal planning began. The process ran four formats across three neighborhoods: moderated neighborhood walkshops, thematic workshops and planning roundtables, online map based feedback tools, and targeted dialogue with local businesses on delivery and loading needs. Resident input was cross validated against traffic counts, video observation, and GIS crash heatmaps, then translated by planners into implementable designs.
+Why: Wrong-source content: the participatory cells describe a German Kiezblock co-production study that does not exist in Di Ruocco. The paper is explicitly a literature review. Verified by keyword search (Pankow/Kiezblock/Winsviertel/Gruene Stadt = 0 hits) despite the cells citing specific pages.</t>
       </text>
     </comment>
-    <comment ref="M17" authorId="0" shapeId="0">
+    <comment ref="P20" authorId="0" shapeId="0">
       <text>
-        <t>Original: "a near-absence of meaningful public involvement through which affected residents can influence and shape decisions" (p. 2).
-Why: The quote is verbatim and on p. 2, but the source file is the author preprint manuscript (KarnerMarcantonio_PWMP_preprint.pdf), not the published article. Since the row cites the published Public Works Management &amp; Policy DOI, a reader checking p. 2 of the journal version will not find this text. Naming the preprint keeps the page cite honest.</t>
+        <t>Original: Combining resident input with independent traffic observation let planners compensate for uneven turnout. In the lower engagement Gruene Stadt neighborhood, systematic traffic counts filled gaps left by weaker civic participation, while the high turnout Winsviertel produced detailed, well contextualized proposals (p. 4). Translating residents' ambitious asks, like full street closures, into a legally defensible package of selective modal filters and school street timing preserved core safety goals while demonstrating responsiveness, which helped stabilize support (p. 6).
+Why: The prior 'What worked' text (Gruene Stadt traffic counts, Winsviertel proposals, p. 4 and p. 6) belongs to a different paper's Kiezblock case study, not this literature review. As a review of others' work with no participatory process of its own, the honest value is N/A.</t>
       </text>
     </comment>
-    <comment ref="M20" authorId="0" shapeId="0">
+    <comment ref="Q20" authorId="0" shapeId="0">
       <text>
-        <t>Original: "this would not have happened" (p. 11).
-Why: The original quote is verbatim and correctly placed on p. 11, but five generic words carry no meaning on their own: a reader scanning the tracker cannot tell what would not have happened. The fuller sentence on p. 11 names the youth-led project and the state agency, which is the concrete mobility example the row's Relevance column depends on.</t>
-      </text>
-    </comment>
-    <comment ref="M22" authorId="0" shapeId="0">
-      <text>
-        <t>Original: "Who is the built world built for?" (p. 15).
-Why: Citation integrity: the quote is verbatim on p. 15, but the book attributes the question to Hendren (2020). As originally written the row reads as Jensen's own phrasing. The quote stays, the nested source is now named.</t>
-      </text>
-    </comment>
-    <comment ref="M24" authorId="0" shapeId="0">
-      <text>
-        <t>Original: "Politicians come and go. They have priorities" (p. 7).
-Why: The original is verbatim and on p. 7, but it stops mid-sentence at 'They have priorities', which states nothing on its own. The rest of the participant's sentence carries the actual finding, that political priorities do not match stakeholders' priorities, which is what the row's Value foreclosed and Relevance columns rely on.</t>
-      </text>
-    </comment>
-    <comment ref="K27" authorId="0" shapeId="0">
-      <text>
-        <t>Original: Directly supports the infrastructure without participation reproduces exclusion half with a documented example: a Virginia DOT advisory committee that shrank from 70 interested citizens to about 30 hand-picked representatives, held up in agency literature as a model process despite excluding most of the public who showed up.
-Why: No-fabrication check: the original states the committee 'shrank from 70 interested citizens to about 30 hand-picked representatives', but the paper never gives a resulting committee size. Page 16 supports 'nearly 70 people showed up' and the instruction to nominate 'only one or two persons' per organization, so the figure 'about 30' is unsupported by the source and is removed here.</t>
-      </text>
-    </comment>
-    <comment ref="M31" authorId="0" shapeId="0">
-      <text>
-        <t>Original: "a fundamental mismatch between who is making key transit decisions . . . and who is most affected by those decisions" (p. 2).
-Why: Citation integrity: the quote is verbatim on p. 2, ellipsis included, but the paper attributes it to TransitCenter (2022, p. 5). As originally written the row reads as the authors' own formulation. The quote stays, the nested source is now named.</t>
-      </text>
-    </comment>
-    <comment ref="C32" authorId="0" shapeId="0">
-      <text>
-        <t>Original: 2026
-Why: The source does not support 2026. This PDF is an article in press (volume line reads 'xxx (xxxx) xxx'), and the only dates printed are 'Received 23 June 2024, Received in revised form 5 June 2025, Accepted 17 July 2025', with DOI 10.1016/j.ijtst.2025.07.009. No 2026 appears anywhere in the document. If the article later appeared in a 2026 issue, confirm from the publisher page and keep 2026; otherwise 2025 is what the source shows.</t>
-      </text>
-    </comment>
-    <comment ref="M36" authorId="0" shapeId="0">
-      <text>
-        <t>Original: "it is often pro forma, and its results are unlikely to affect ultimate decisions" (p. 3).
-Why: The quote is verbatim and on p. 3, but the source file (dot_67311_DS1.pdf) is the author manuscript, not the typeset article: page 1 carries a running head and author contact block rather than journal pagination. Since the row cites the published Journal of Planning Literature DOI, a reader checking p. 3 of the journal version will not find this text. Same issue as the Karner et al. 2017 row.</t>
+        <t>Original: Several of the most ambitious civic proposals, area wide modal filters and full street closures, exceeded what the district could enact under existing German road traffic regulations, forcing scaled back compromises (p. 6). Even empirically justified measures still met individual resistance from residents, particularly older residents worried about parking or navigation, showing shared data could not resolve disagreements rooted in values and interests, and that legitimacy required continuous negotiation rather than being automatically produced by participation (p. 6).
+Why: The prior 'What didn't work' text (modal filters, full street closures blocked by German road traffic regulations, p. 6) belongs to the same misattributed Kiezblock case study, not to Di Ruocco. Corrected to N/A for a literature review.</t>
       </text>
     </comment>
   </commentList>
@@ -501,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:Q40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -518,96 +482,194 @@
     <col width="32" customWidth="1" min="12" max="12"/>
     <col width="32" customWidth="1" min="13" max="13"/>
     <col width="32" customWidth="1" min="14" max="14"/>
+    <col width="32" customWidth="1" min="15" max="15"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Community &amp; Equity Dimensions of Mobility Literature Review</t>
+          <t>Paper Title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Author(s)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Journal or Proceedings</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>DOI or URL</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Sub-theme</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Central claim</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Key concepts or framework</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Who is centered</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Value foreclosed (community value left out)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Relevance to argument</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Gap or limitation</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Quotable moment</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Synthesis paragraph</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Codesign/participatory method</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>What worked</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>What didn't work</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Paper Title</t>
+          <t>"The bus is accessible, but how do you get to the bus": First and last mile experiences of disabled transit riders</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Author(s)</t>
+          <t>Levine</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Year</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Journal or Proceedings</t>
+          <t>Journal of Public Transportation, 26, 100086</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>DOI or URL</t>
+          <t>https://doi.org/10.1016/j.jpubtr.2024.100086</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sub-theme</t>
+          <t>Disability, first/last mile access</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Central claim</t>
+          <t>Disabled transit riders in Austin and Seattle face similar first and last mile barriers despite different transit systems and geographies, shaped by intersectionality, social context, built environment quality, confidence, and relationships with public agencies. Disabled voices are systematically excluded from planning, perpetuating inequitable outcomes.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Key concepts or framework</t>
+          <t>Mobility justice: multi-scalar framework examining how the built environment reproduces privilege and power beyond basic accessibility. First and last mile: trip segments connecting riders to fixed transit, where accessibility gaps concentrate. Intersectionality: overlapping identities shaping distinct travel burdens.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Who is centered</t>
+          <t>Sixteen disabled transit riders in Austin and Seattle, recruited through disability advocacy organizations, centered through first-person interview accounts.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Value foreclosed (community value left out)</t>
+          <t>Equitable access and flexibility for variable need: ADA compliance measures and stop-count accessibility metrics ignore first and last mile segments and diverse disability needs.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Relevance to argument</t>
+          <t>Supports both halves of the claim. Mobility access is unevenly distributed by disability type, gender, and race even in cities with strong accessibility investment, and infrastructure built to minimum ADA standards without disabled riders' participation reproduces exclusion along the first and last mile. Participants report being seldom in the room when transportation decisions are made, and describe the active transportation engagement process itself as white and male dominated.</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Gap or limitation</t>
+          <t>The sample was recruited through advocacy networks and email, skewing toward riders already engaged with accessibility issues and excluding disabled people without internet access.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Quotable moment</t>
+          <t>"The bus is accessible, but how do you get to the bus?" (p. 5).</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Synthesis paragraph</t>
+          <t>This paper grounds both the uneven distribution and exclusion-from-participation claims in first-person accounts, showing that even accessibility-focused cities produce disproportionate travel burdens when planners ignore first and last mile segments and exclude disabled riders from decision-making. It argues meaningful engagement, not compliance alone, is necessary for equitable mobility infrastructure.</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Semi-structured qualitative interviews with 16 disabled transit riders in Austin and Seattle (Sept to Dec 2022), recruited via purposive and snowball sampling through disability and transit advocacy organizations, community centers, and agency advisory committees. Interviews ran 30 to 60 minutes over Zoom, were transcribed and inductively coded with peer reviewed reliability checks. Consultative research design that elicits lived experience testimony for the author's own analysis, not a process giving participants decision making authority.</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Recruiting through established disability advocacy organizations and agency advisory committees reached participants already embedded in first and last mile issues and yielded rich testimony. Flexible virtual scheduling and letting participants self identify their disability rather than sorting them into researcher defined categories surfaced experiences standard categories miss (p. 4).</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>The author acknowledges recruiting through advocacy networks and email skewed the sample toward already engaged, more aware individuals and excluded disabled people without internet access (p. 4). Participants also described agency led engagement pilots that solicited community input and co-creation but went silent afterward, one saying of a transit pilot, "you hear nothing" once it ended (p. 6).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>"The bus is accessible, but how do you get to the bus": First and last mile experiences of disabled transit riders</t>
+          <t>Public transport inclusion and active aging: A systematic review on elderly mobility</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Levine</t>
+          <t>Zhang et al.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,69 +679,84 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Journal of Public Transportation, 26, 100086</t>
+          <t>Journal of Traffic and Transportation Engineering (English Edition), 11(2), 312-347</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.jpubtr.2024.100086</t>
+          <t>https://doi.org/10.1016/j.jtte.2024.04.001</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Disability, first/last mile access</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Disabled transit riders in Austin and Seattle face similar first and last mile barriers despite different transit systems and geographies, shaped by intersectionality, social context, built environment quality, confidence, and relationships with public agencies. Disabled voices are systematically excluded from planning, perpetuating inequitable outcomes.</t>
+          <t>Elderly mobility, transport inclusion</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>A systematic review of 138 papers finds the elderly experience the highest inequality in public transport resource distribution among disadvantaged traveler groups. It synthesizes a four part framework, opportunity accessibility, physical accessibility, age friendly informationalization, and cost affordability, for transport inclusion policy.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Mobility justice: multi-scalar framework examining how the built environment reproduces privilege and power beyond basic accessibility. First and last mile: trip segments connecting riders to fixed transit, where accessibility gaps concentrate. Intersectionality: overlapping identities shaping distinct travel burdens.</t>
+          <t>Transport related social exclusion: marginalization from daily activities caused by inadequate transport across accessibility, physical, information, and economic dimensions. Capability approach: evaluates inclusion by whether services convert into real capabilities. Spatial production theory: transport spaces shape perceived social inclusion.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Sixteen disabled transit riders in Austin and Seattle, recruited through disability advocacy organizations, centered through first-person interview accounts.</t>
+          <t>The perspective of transport planners and policymakers, synthesized through published research rather than elderly travelers' own accounts.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Equitable access and flexibility for variable need: ADA compliance measures and stop-count accessibility metrics ignore first and last mile segments and diverse disability needs.</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Supports both halves of the claim. Mobility access is unevenly distributed by disability type, gender, and race even in cities with strong accessibility investment, and infrastructure built to minimum ADA standards without disabled riders' participation reproduces exclusion along the first and last mile. Participants report being seldom in the room when transportation decisions are made, and describe the active transportation engagement process itself as white and male dominated.</t>
+          <t>Relational trust and flexibility for variable need: the framework measures inclusion through accessibility and cost metrics rather than relationships or elderly travelers' own participation in defining inclusion.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Supports the unevenly distributed half directly, documenting that elderly people face the highest transport resource inequality among disadvantaged groups across three decades of research. It does not address community participation in infrastructure decisions: its own framework is top down and metric driven, built from published literature rather than elderly travelers' input, making it a thinner fit for the infrastructure without participation half of the claim.</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>The sample was recruited through advocacy networks and email, skewing toward riders already engaged with accessibility issues and excluding disabled people without internet access.</t>
+          <t>The evaluation framework assumes public transit dependent cities and fits poorly in car dependent or rural contexts, and it pools evidence on other disadvantaged groups without a participatory method to test the framework directly.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>"The bus is accessible, but how do you get to the bus?" (p. 5).</t>
+          <t>"the elderly have the highest level of inequality in PT resource distribution" (p. 2).</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>This paper grounds both the uneven distribution and exclusion-from-participation claims in first-person accounts, showing that even accessibility-focused cities produce disproportionate travel burdens when planners ignore first and last mile segments and exclude disabled riders from decision-making. It argues meaningful engagement, not compliance alone, is necessary for equitable mobility infrastructure.</t>
+          <t>This review documents that elderly people face the steepest transport inequality among disadvantaged groups, giving quantitative backing to the claim that mobility access has long been unevenly distributed. Its own accessibility centered framework, however, is built from literature rather than elderly voices, illustrating by contrast why participatory approaches matter for defining what inclusion requires.</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>None described. This is a top down synthesis of 138 published studies rather than the authors' own fieldwork; it notes in passing that some reviewed studies used focus groups or in depth interviews as a data collection method, but gives no detail on who was involved, how, or with what outcome.</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Public transport inclusion and active aging: A systematic review on elderly mobility</t>
+          <t>Bridging the gap: Do community needs assessments enhance public participation in transportation planning?</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Zhang et al.</t>
+          <t>Pinski et al.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -689,69 +766,84 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Journal of Traffic and Transportation Engineering (English Edition), 11(2), 312-347</t>
+          <t>Transportation Research Interdisciplinary Perspectives, 25, 101114</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.jtte.2024.04.001</t>
+          <t>https://doi.org/10.1016/j.trip.2024.101114</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Elderly mobility, transport inclusion</t>
+          <t>Community needs assessments</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>A systematic review of 138 papers finds the elderly experience the highest inequality in public transport resource distribution among disadvantaged traveler groups. It synthesizes a four part framework, opportunity accessibility, physical accessibility, age friendly informationalization, and cost affordability, for transport inclusion policy.</t>
+          <t>California's community transportation needs assessment pilot program, intended to include historically underrepresented groups in transportation planning, largely reproduced the same representation gaps and engagement shortfalls as traditional public participation processes.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Transport related social exclusion: marginalization from daily activities caused by inadequate transport across accessibility, physical, information, and economic dimensions. Capability approach: evaluates inclusion by whether services convert into real capabilities. Spatial production theory: transport spaces shape perceived social inclusion.</t>
+          <t>Community transportation needs assessment: a grassroots funded study meant to engage underrepresented residents in identifying transportation needs. Representation gap: participants in planning processes skew older, whiter, and more affluent than the community. Tokenism: participation that solicits input without incorporating it into decisions.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>The perspective of transport planners and policymakers, synthesized through published research rather than elderly travelers' own accounts.</t>
+          <t>Local organizations and residents surveyed under California's Clean Mobility Options pilot, analyzed through awardees' final reports and survey data rather than participant narratives.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Relational trust and flexibility for variable need: the framework measures inclusion through accessibility and cost metrics rather than relationships or elderly travelers' own participation in defining inclusion.</t>
+          <t>Equitable access: even purpose built participatory processes struggled to reach disadvantaged and hard to reach populations, leaving the same groups underrepresented as in conventional public meetings.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Supports the unevenly distributed half directly, documenting that elderly people face the highest transport resource inequality among disadvantaged groups across three decades of research. It does not address community participation in infrastructure decisions: its own framework is top down and metric driven, built from published literature rather than elderly travelers' input, making it a thinner fit for the infrastructure without participation half of the claim.</t>
+          <t>Directly supports the infrastructure without participation reproduces exclusion half of the claim. It shows that even funded, explicitly inclusive community needs assessments replicate historic representation gaps rather than closing them, and traces this pattern back to the 1950s and 1960s highway projects that displaced low income and Black residents with little say in the process.</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>The evaluation framework assumes public transit dependent cities and fits poorly in car dependent or rural contexts, and it pools evidence on other disadvantaged groups without a participatory method to test the framework directly.</t>
+          <t>The study cannot confirm whether any assessment's recommendations changed actual transportation plans or funding, and it analyzes only California's pilot program, limiting generalizability to other participatory models.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>"the elderly have the highest level of inequality in PT resource distribution" (p. 2).</t>
+          <t>"urban renewal projects of the 1950s and 1960s that displaced more than 1 million Americans, residents that were disproportionately low-income and Black" (p. 2).</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>This review documents that elderly people face the steepest transport inequality among disadvantaged groups, giving quantitative backing to the claim that mobility access has long been unevenly distributed. Its own accessibility centered framework, however, is built from literature rather than elderly voices, illustrating by contrast why participatory approaches matter for defining what inclusion requires.</t>
+          <t>Even when agencies fund grassroots, explicitly inclusive needs assessments, this study finds they largely reproduce the same representation gaps as traditional public meetings. It underscores that participation structures, not just their existence, determine whether infrastructure decisions genuinely include disadvantaged communities, grounding the section's exclusion claim in a contemporary case rather than only historical precedent.</t>
+        </is>
+      </c>
+      <c r="O4" s="1" t="inlineStr">
+        <is>
+          <t>Secondary comparative analysis, not the authors' own fieldwork, of the 24 California Clean Mobility Options community transportation needs assessment awardees' final reports and survey data, benchmarked against long range transportation plans' public participation records. Awardees used varied methods: surveys, workshops, focus groups, interviews, community meetings, stakeholder phone calls, photovoice, collaborative mapping, and one virtual reality component, often co hosted with community based organizations. The authors evaluate whether these funded, explicitly inclusive processes reached and empowered underrepresented residents, not whether their own study did.</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Awardees that met residents where they already gathered, such as churches, food distribution lines, or parent nights, and organizations with pre-existing trust or ties to community groups generated stronger turnout than cold outreach. Hiring local staff, using experienced consultants, and targeting small, tightly networked populations like tribes improved response and demographic reach. A consultant on staff nearly tripled the population adjusted response rate (p. 5-6).</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Snowball sampling and mailed flyers mostly reached people already engaged, and events requiring travel or extra time suppressed turnout even when reach was high. Awardees rarely tracked participant demographics, especially for focus groups and interviews, so several could not confirm representativeness. One awardee's own report admitted its focus group participants "appeared to be primarily white and older" despite not collecting that data (p. 6). Targeted groups like unemployed or youth residents stayed underrepresented regardless of method.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bridging the gap: Do community needs assessments enhance public participation in transportation planning?</t>
+          <t>Moving Towards Mobility Justice: Challenges and Considerations for Supporting Advocacy</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pinski et al.</t>
+          <t>Agrawaal et al.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -761,645 +853,780 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Transportation Research Interdisciplinary Perspectives, 25, 101114</t>
+          <t>Proc. ACM Hum.-Comput. Interact., 8(CSCW1), Article 96</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.trip.2024.101114</t>
+          <t>https://doi.org/10.1145/3637373</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Community needs assessments</t>
+          <t>Mobility justice advocacy</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>California's community transportation needs assessment pilot program, intended to include historically underrepresented groups in transportation planning, largely reproduced the same representation gaps and engagement shortfalls as traditional public participation processes.</t>
+          <t>Interviews with Canadian transportation advocates identify four ways that mobility planning tools and information systems deepen the divide between planners and the public. Path dependence in transportation knowledge infrastructures is a systemic barrier to overcoming these mobility injustices.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Community transportation needs assessment: a grassroots funded study meant to engage underrepresented residents in identifying transportation needs. Representation gap: participants in planning processes skew older, whiter, and more affluent than the community. Tokenism: participation that solicits input without incorporating it into decisions.</t>
+          <t>Mobility justice: Sheller's framework analyzing interacting relations of movement, dividing populations into kinetic elite and mobility poor. Path dependence: how the historical design of planning tools locks in and perpetuates exclusion. Data infrastructure literacy: sensitivity to the social and political contexts data is embedded in.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Local organizations and residents surveyed under California's Clean Mobility Options pilot, analyzed through awardees' final reports and survey data rather than participant narratives.</t>
+          <t>Mobility justice advocates and community organizers across Canada, centered through their own accounts of interacting with planning technologies and processes.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Equitable access: even purpose built participatory processes struggled to reach disadvantaged and hard to reach populations, leaving the same groups underrepresented as in conventional public meetings.</t>
+          <t>Equitable access and relational trust: technical, jargon heavy planning tools and English only materials exclude non expert and non English speaking residents from decisions imposed on them.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Directly supports the infrastructure without participation reproduces exclusion half of the claim. It shows that even funded, explicitly inclusive community needs assessments replicate historic representation gaps rather than closing them, and traces this pattern back to the 1950s and 1960s highway projects that displaced low income and Black residents with little say in the process.</t>
+          <t>Directly supports the infrastructure without participation reproduces exclusion half. Advocates describe how technically inaccessible tools, English only materials, and planners' hyper focus on traffic counts over lived experience shut residents out of decisions, echoing the historical divide between the kinetic elite and the mobility poor that mobility justice scholarship names.</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>The study cannot confirm whether any assessment's recommendations changed actual transportation plans or funding, and it analyzes only California's pilot program, limiting generalizability to other participatory models.</t>
+          <t>The sample is limited to advocacy organizations already engaged in mobility justice work in Canada, so it may not capture residents who never reach an advocacy organization at all.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>"urban renewal projects of the 1950s and 1960s that displaced more than 1 million Americans, residents that were disproportionately low-income and Black" (p. 2).</t>
+          <t>"a conversation that only some people are allowed to be in" (p. 8).</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Even when agencies fund grassroots, explicitly inclusive needs assessments, this study finds they largely reproduce the same representation gaps as traditional public meetings. It underscores that participation structures, not just their existence, determine whether infrastructure decisions genuinely include disadvantaged communities, grounding the section's exclusion claim in a contemporary case rather than only historical precedent.</t>
+          <t>This paper grounds the exclusion half of the claim in current advocacy work, showing that technical jargon, English only materials, and planners' narrow traffic metrics reproduce the same divide between decision makers and residents that mobility justice scholarship critiques historically. It introduces path dependence as a mechanism for why exclusionary infrastructure persists.</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>The authors' own method is 16 semi-structured interviews with senior figures at Canadian mobility justice organizations, recruited via civic technology groups, snowball sampling, and personal contacts between June and September 2022, conducted over Zoom, 45 to 60 minutes, analyzed via two coder reflective thematic analysis. Substantively, interviewees describe two separate participatory practices as their advocacy subject matter: municipal public participation via city planning meetings and town halls, and advocacy led community outreach such as temporary pop up demonstrations. These are the interviewees' accounts of processes the authors did not run themselves.</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Advocacy organizations' own outreach, not the cities', is what interviewees describe succeeding. Temporary pop up demonstrations of mobility solutions paired with deliberate storytelling messaging that frames changes as a reversible pilot built resident buy in and reduced resistance to proposed changes (p. 8).</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Interviewees describe municipal public participation through city planning meetings and town halls as excluding residents through technical, jargon heavy proposals, with one advocate calling it "a conversation that only some people are allowed to be in" (p. 8). Everyday transit information and outreach materials being English only, despite roughly 50 languages spoken in Toronto, further shut out non-English speaking riders from participating (p. 8).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Moving Towards Mobility Justice: Challenges and Considerations for Supporting Advocacy</t>
+          <t>Co-Creating Accessibility-Centred Mobility Strategies in Low-Density Suburban Contexts: Evidence from Coimbra, Portugal</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Agrawaal et al.</t>
+          <t>Gomes et al.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Proc. ACM Hum.-Comput. Interact., 8(CSCW1), Article 96</t>
+          <t>Urban Science, 10(2), 102</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1145/3637373</t>
+          <t>https://doi.org/10.3390/urbansci10020102</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mobility justice advocacy</t>
+          <t>Co-creation in suburban mobility</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Interviews with Canadian transportation advocates identify four ways that mobility planning tools and information systems deepen the divide between planners and the public. Path dependence in transportation knowledge infrastructures is a systemic barrier to overcoming these mobility injustices.</t>
+          <t>Three co-creation focus groups with institutional, technical, and citizen actors in a low-density Portuguese suburb produced eight collaboratively defined mobility strategies spanning pedestrian and cycling infrastructure, transit reliability, and governance. Accessibility, inclusiveness, and institutional coordination emerge as interdependent conditions for equitable mobility transitions.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Mobility justice: Sheller's framework analyzing interacting relations of movement, dividing populations into kinetic elite and mobility poor. Path dependence: how the historical design of planning tools locks in and perpetuates exclusion. Data infrastructure literacy: sensitivity to the social and political contexts data is embedded in.</t>
+          <t>15-Minute City, Transit-Oriented Development, and Mobility as a Service: proximity based planning paradigms reinterpreted by participants as functional access goals rather than fixed density templates. Co-creation: focus group based collective strategy building across institutional, technical, and citizen stakeholders.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Mobility justice advocates and community organizers across Canada, centered through their own accounts of interacting with planning technologies and processes.</t>
+          <t>Institutional, technical, and citizen actors in Sao Martinho do Bispo, a low-density Coimbra suburb, though citizen participants were predominantly older adults.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Equitable access and relational trust: technical, jargon heavy planning tools and English only materials exclude non expert and non English speaking residents from decisions imposed on them.</t>
+          <t>Flexibility for variable need: participants were predominantly older adults, so younger low-income residents, migrants, and people with disabilities were underrepresented in shaping the co-created strategies.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Directly supports the infrastructure without participation reproduces exclusion half. Advocates describe how technically inaccessible tools, English only materials, and planners' hyper focus on traffic counts over lived experience shut residents out of decisions, echoing the historical divide between the kinetic elite and the mobility poor that mobility justice scholarship names.</t>
+          <t>Directly supports the infrastructure without participation reproduces exclusion half, showing that treating proximity-based models like the 15-Minute City and TOD as co-created rather than fixed templates surfaces needs, such as trust in transit reliability and safe pedestrian access, that top down planning alone would miss.</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>The sample is limited to advocacy organizations already engaged in mobility justice work in Canada, so it may not capture residents who never reach an advocacy organization at all.</t>
+          <t>The case draws on a single suburb and a limited number of focus groups skewed toward older participants, so the strategies are preliminary and unvalidated against underrepresented groups' needs.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>"a conversation that only some people are allowed to be in" (p. 8).</t>
+          <t>"key to rebuilding trust in public transport" (p. 22).</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>This paper grounds the exclusion half of the claim in current advocacy work, showing that technical jargon, English only materials, and planners' narrow traffic metrics reproduce the same divide between decision makers and residents that mobility justice scholarship critiques historically. It introduces path dependence as a mechanism for why exclusionary infrastructure persists.</t>
+          <t>This case shows that participatory reinterpretation of proximity based planning models, rather than top down application, is what surfaces suburban residents' actual priorities, though the strategies here reflect mostly older adults and remain unvalidated. It offers a concrete example of co-creation as a mechanism for avoiding exclusionary infrastructure.</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Three deliberative focus groups in Sao Martinho do Bispo, Coimbra (March to April 2025) with 18 institutional, technical, and citizen participants, recruited through local associations, municipal contacts, and institutional partnerships. Institutional and citizen stakeholders met in separate sessions to reduce power asymmetries. A four phase structure moved from trust building to mapping priorities, generating individual proposals, and collectively assessing and co creating eight territorial strategies. Sessions were recorded, transcribed, and analyzed with co-occurrence coding. Consultative and advisory: the co created strategies are framed as preliminary inputs needing further validation, not binding decisions.</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Separating institutional/technical and citizen groups let citizens articulate everyday constraints without institutional influence and let officials speak candidly about feasibility, reducing power asymmetries (p. 8). The structured four phase deliberation and co-design process was described as transformative, with participants moving beyond identifying barriers to collectively reframing mobility as a shared public responsibility (p. 24).</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Citizen participants skewed toward older adults reflecting the area's demographics, likely underrepresenting younger, low income, migrant, or disabled residents. Recruitment was also constrained by limited availability and willingness to participate in this car dependent suburb (p. 27). The authors caution that subtle institutional framing was not fully eliminated despite group separation, and the co created strategies remain unvalidated proposals, not implementation commitments (p. 27).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Co-Creating Accessibility-Centred Mobility Strategies in Low-Density Suburban Contexts: Evidence from Coimbra, Portugal</t>
+          <t>Toward Structured Public Involvement: Justice, Geography and Collaborative Geospatial/Geovisual Decision Support Systems</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Gomes et al.</t>
+          <t>Bailey et al.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Urban Science, 10(2), 102</t>
+          <t>Annals of the Association of American Geographers, 100(1), 57-86</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/urbansci10020102</t>
+          <t>https://doi.org/10.1080/00045600903364259</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Co-creation in suburban mobility</t>
+          <t>Structured public involvement</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Three co-creation focus groups with institutional, technical, and citizen actors in a low-density Portuguese suburb produced eight collaboratively defined mobility strategies spanning pedestrian and cycling infrastructure, transit reliability, and governance. Accessibility, inclusiveness, and institutional coordination emerge as interdependent conditions for equitable mobility transitions.</t>
+          <t>Surveys of transportation professionals and the public reveal an Arnstein Gap, a persistent difference between the public involvement stakeholders experience and what they want in transportation infrastructure planning. The paper proposes structured public involvement, using geovisual decision support tools, to narrow this gap without requiring full consensus.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>15-Minute City, Transit-Oriented Development, and Mobility as a Service: proximity based planning paradigms reinterpreted by participants as functional access goals rather than fixed density templates. Co-creation: focus group based collective strategy building across institutional, technical, and citizen stakeholders.</t>
+          <t>Arnstein Gap: the measured difference between perceived and desired public involvement on Arnstein's ladder of citizen participation. Structured public involvement: a reflexive, nonconsensual framework using geovisual tools to elicit and respect community cultural values. Procedural justice: attaining spatial justice through fair process rather than fair distribution alone.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Institutional, technical, and citizen actors in Sao Martinho do Bispo, a low-density Coimbra suburb, though citizen participants were predominantly older adults.</t>
+          <t>Transportation professionals and public stakeholders surveyed across Kentucky, Indiana, Arizona, and Alaska, compared to reveal gaps in perceived versus desired involvement.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Flexibility for variable need: participants were predominantly older adults, so younger low-income residents, migrants, and people with disabilities were underrepresented in shaping the co-created strategies.</t>
+          <t>Relational trust: surveyed professionals showed a professional conceit, believing public involvement worked better than the public itself reported, reflecting distrust that constrains genuine collaboration.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Directly supports the infrastructure without participation reproduces exclusion half, showing that treating proximity-based models like the 15-Minute City and TOD as co-created rather than fixed templates surfaces needs, such as trust in transit reliability and safe pedestrian access, that top down planning alone would miss.</t>
+          <t>Directly supports the infrastructure without participation reproduces exclusion half. The Arnstein Gap quantifies a persistent, measured shortfall in transportation infrastructure decision making that professionals do not fully recognize, and the paper argues this gap is structural to U.S. transportation planning rather than an occasional failure.</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>The case draws on a single suburb and a limited number of focus groups skewed toward older participants, so the strategies are preliminary and unvalidated against underrepresented groups' needs.</t>
+          <t>The survey based Arnstein Gap metric captures perceived involvement levels but not whether structured public involvement deployments change actual infrastructure outcomes, and the case studies are limited to a handful of U.S. states.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>"key to rebuilding trust in public transport" (p. 22).</t>
+          <t>"The Arnstein Gap indicates that the public desire a TI planning and design system that is more directly responsive to public needs" (p. 7).</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>This case shows that participatory reinterpretation of proximity based planning models, rather than top down application, is what surfaces suburban residents' actual priorities, though the strategies here reflect mostly older adults and remain unvalidated. It offers a concrete example of co-creation as a mechanism for avoiding exclusionary infrastructure.</t>
+          <t>This paper offers historical and methodological grounding for why participation gaps in infrastructure planning persist, showing empirically that professionals underestimate the disconnect between desired and actual public involvement. It supports treating infrastructure without participation as a structural, measurable problem, and frames a participatory alternative that need not require full consensus to be legitimate.</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Reviews two of the authors' own structured public involvement (SPI) case studies embedded within standard public meetings on U.S. highway projects, up to 300 attendees per event. AMIS is a facilitated GIS and multicriteria corridor evaluation eliciting stakeholder impedance values for landscape features via focus group meetings and AHP weighting, applied to a Kentucky highway corridor. CAVE is a fuzzy logic Likert scale visual preference survey scoring twenty to thirty design visualizations per two hour session, applied to noise wall and bridge design. Anonymous, simultaneous, one person one input scoring reduces strategic behavior, framed as consultative input into decisions agencies still make.</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Anonymous input collection surfaced concerns officials did not know existed. A Kentucky caving group's data on cave locations and recreational value, gathered confidentially through AMIS, reshaped the corridor route once engineers saw it (p. 18). SPI fit inside existing public meetings rather than requiring extra ones, which lowered sponsors' and professionals' resistance to adopting it and let large crowds participate on equal footing (p. 23).</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>The research team never held direct power to guarantee designs got built, and performance still partly reflected each project sponsor's preferred Arnstein Ladder position, meaning agencies could still limit how much influence input carried (p. 23). CAVE's format caps meetings at roughly twenty to thirty scoreable images in two hours, too few for reliable statistical analysis, and the authors concede SPI does not resolve whether attendees are a representative sample of the public (p. 19, 23).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Toward Structured Public Involvement: Justice, Geography and Collaborative Geospatial/Geovisual Decision Support Systems</t>
+          <t>Centering disability justice in active transportation transitions: A conceptual counter-cartography</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bailey et al.</t>
+          <t>Soliz et al.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Annals of the Association of American Geographers, 100(1), 57-86</t>
+          <t>Transportation Research Interdisciplinary Perspectives, 36, 101805</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/00045600903364259</t>
+          <t>https://doi.org/10.1016/j.trip.2025.101805</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Structured public involvement</t>
+          <t>Disability justice, active transportation</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Surveys of transportation professionals and the public reveal an Arnstein Gap, a persistent difference between the public involvement stakeholders experience and what they want in transportation infrastructure planning. The paper proposes structured public involvement, using geovisual decision support tools, to narrow this gap without requiring full consensus.</t>
+          <t>Twenty interviews with disabled people in Montreal and a conceptual counter-cartography approach show that dominant definitions of active travel, limited to biking and walking on foot, exclude wheelchair, scooter, and adapted cycle users. The paper argues infrastructure should center disability justice and disabled people's leadership rather than retrofit universal design standards.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Arnstein Gap: the measured difference between perceived and desired public involvement on Arnstein's ladder of citizen participation. Structured public involvement: a reflexive, nonconsensual framework using geovisual tools to elicit and respect community cultural values. Procedural justice: attaining spatial justice through fair process rather than fair distribution alone.</t>
+          <t>Counter-cartography: a mapping method layering policy definitions against interview accounts to expose whose mobility practices get excluded. Disability justice: a framework centering disabled people's leadership, distinct from accommodation focused universal design. Crip time: reframing infrastructure to bend to disabled bodies' pace rather than the reverse.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Transportation professionals and public stakeholders surveyed across Kentucky, Indiana, Arizona, and Alaska, compared to reveal gaps in perceived versus desired involvement.</t>
+          <t>Twenty people with disabilities in Montreal, interviewed about their own active travel practices and infrastructure needs.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Relational trust: surveyed professionals showed a professional conceit, believing public involvement worked better than the public itself reported, reflecting distrust that constrains genuine collaboration.</t>
+          <t>Flexibility for variable need: Montreal's official definitions of active travel as biking or walking on foot formally exclude wheelchairs, scooters, and adapted cycles from infrastructure meant to serve them.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Directly supports the infrastructure without participation reproduces exclusion half. The Arnstein Gap quantifies a persistent, measured shortfall in transportation infrastructure decision making that professionals do not fully recognize, and the paper argues this gap is structural to U.S. transportation planning rather than an occasional failure.</t>
+          <t>Directly supports the infrastructure without participation reproduces exclusion half. Montreal's own policy definitions of active travel exclude many disabled people's actual mobility practices, and interviewees describe cycling infrastructure too narrow for tricycles and adapted cycles, showing how planning built without disabled people's input structurally forecloses their access.</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>The survey based Arnstein Gap metric captures perceived involvement levels but not whether structured public involvement deployments change actual infrastructure outcomes, and the case studies are limited to a handful of U.S. states.</t>
+          <t>The study draws on 20 interviews in a single city, and the authors call for broader research across more disability communities to inform infrastructural design processes.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>"The Arnstein Gap indicates that the public desire a TI planning and design system that is more directly responsive to public needs" (p. 7).</t>
+          <t>"sidewalks hit hard" (p. 6).</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>This paper offers historical and methodological grounding for why participation gaps in infrastructure planning persist, showing empirically that professionals underestimate the disconnect between desired and actual public involvement. It supports treating infrastructure without participation as a structural, measurable problem, and frames a participatory alternative that need not require full consensus to be legitimate.</t>
+          <t>This paper shows that official definitions of active travel, not just physical infrastructure, can foreclose disabled people's access, since Montreal's own policy language excludes many disabled mobility practices before infrastructure is even built. It reinforces that centering disabled people's expertise and leadership, not only accommodation, is necessary for genuinely inclusive infrastructure decisions.</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>The authors' own conceptual counter-cartography method is explicitly participatory: people with disabilities and Quebec disability organizations helped choose methods, design research tools, shape recruitment, and analyze data, not just serve as interview subjects. Core data comes from 20 semi-structured, one to two hour interviews with disabled Montrealers, recruited via stratified purposeful sampling through partner organizations, covering local transportation experiences and public consultation processes, paired with analysis of 15 local active transportation and accessibility policies. Interviewees separately described the city's own public consultation forums for active transportation planning.</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Recruiting through disability partner organizations who helped design the study, not just supply participants, produced a sample spanning a range of disability types, ages, and 11 of Montreal's 19 boroughs. Many interviewees credited the city's cycling network expansion itself as a genuine effort responding to community pressure, even while critiquing its design (p. 4).</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>The authors could not meaningfully include people with intellectual disabilities within this study's methods and are addressing that gap through a separate, adapted participatory project, calling it a key limitation of the findings reported here (p. 4). Interviewees also reported a broader lack of appropriate participation modalities, and of accountability for social inclusion commitments, within Montreal's technical and public consultation forums for transportation planning (p. 5).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Centering disability justice in active transportation transitions: A conceptual counter-cartography</t>
+          <t>Performative versus Authentic Equity Work: An Assessment of Current Practices in Transportation Planning</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Soliz et al.</t>
+          <t>McCullough et al.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Transportation Research Interdisciplinary Perspectives, 36, 101805</t>
+          <t>Transportation Research Record, 2678(5), 884-903</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.trip.2025.101805</t>
+          <t>https://doi.org/10.1177/03611981231193409</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Disability justice, active transportation</t>
+          <t>Performative vs authentic equity</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Twenty interviews with disabled people in Montreal and a conceptual counter-cartography approach show that dominant definitions of active travel, limited to biking and walking on foot, exclude wheelchair, scooter, and adapted cycle users. The paper argues infrastructure should center disability justice and disabled people's leadership rather than retrofit universal design standards.</t>
+          <t>Interviews with 28 Black and people of color transportation professionals in California distinguish performative equity work, which privileges dominant groups' comfort and produces only superficial change, from authentic equity work, which redistributes decision making power and produces measurable change for historically oppressed communities.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Counter-cartography: a mapping method layering policy definitions against interview accounts to expose whose mobility practices get excluded. Disability justice: a framework centering disabled people's leadership, distinct from accommodation focused universal design. Crip time: reframing infrastructure to bend to disabled bodies' pace rather than the reverse.</t>
+          <t>Performative equity work: actions or rhetoric that claim to address equity without materially changing outcomes or power. Authentic equity work: sustained redistribution of funding, time, and decision making power to affected communities. Arrested mobility: policing practices that apprehend or harm Black people simply for moving through public space.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Twenty people with disabilities in Montreal, interviewed about their own active travel practices and infrastructure needs.</t>
+          <t>Twenty eight California transportation professionals who identify as Black, Indigenous, or people of color, centered through their own workplace and policy experiences.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Flexibility for variable need: Montreal's official definitions of active travel as biking or walking on foot formally exclude wheelchairs, scooters, and adapted cycles from infrastructure meant to serve them.</t>
+          <t>Relational trust and equitable access: performative equity work keeps decision making power concentrated among historically dominant, often white leadership, even while claiming to value equity, leaving communities without real control over resources.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Directly supports the infrastructure without participation reproduces exclusion half. Montreal's own policy definitions of active travel exclude many disabled people's actual mobility practices, and interviewees describe cycling infrastructure too narrow for tricycles and adapted cycles, showing how planning built without disabled people's input structurally forecloses their access.</t>
+          <t>Supports both halves of the claim. It documents uneven distribution of power and voice among transportation professionals of color within the field itself, and argues that infrastructure and funding decisions made without genuinely redistributing power to communities, not just consulting them, reproduce the same exclusion regardless of stated equity commitments.</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>The study draws on 20 interviews in a single city, and the authors call for broader research across more disability communities to inform infrastructural design processes.</t>
+          <t>The study is limited to California and did not achieve representation from Indigenous or tribal transportation professionals despite specific recruitment efforts, limiting the framework's tested scope.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>"sidewalks hit hard" (p. 6).</t>
+          <t>"Many communities know the solutions to the challenges they face" (p. 12).</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>This paper shows that official definitions of active travel, not just physical infrastructure, can foreclose disabled people's access, since Montreal's own policy language excludes many disabled mobility practices before infrastructure is even built. It reinforces that centering disabled people's expertise and leadership, not only accommodation, is necessary for genuinely inclusive infrastructure decisions.</t>
+          <t>This paper reframes community participation as insufficient unless paired with actual redistribution of power and resources, showing that even self identified equity conscious agencies can produce only performative change. It supports the section's exclusion claim by locating the same power imbalance inside the transportation profession itself, not only in public facing planning processes.</t>
+        </is>
+      </c>
+      <c r="O9" s="1" t="inlineStr">
+        <is>
+          <t>The authors' own method is 28 semi-structured interviews with BIPOC transportation professionals, conducted in two rounds between April and August 2020, recruited through referrals and thematically coded, asking how they view equity work in their agencies. Interviewees describe two contrasting community engagement models: performative outreach that checklists community input after decisions are already made, versus a Central Valley group's monthly equity led agenda meetings, where residents envision the community they want, that vision is translated into plans and policies, and organizers then advocate to get those plans implemented so residents benefit from their own feedback.</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>The Central Valley model's recurring monthly meetings, which fed resident visions directly into plans and then into advocacy for implementation, was cited as authentic engagement because residents saw a throughline from input to outcome, not just being heard. Interviewees also stressed that trust building takes ongoing relationships with the most neglected residents, not one time consultation (p. 11).</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Interviewees described performative engagement as checking an outreach box or being brought in only after a project's decisions were already made, calling it a process where feedback "can't really impact much" (p. 11). One professional said real equity means removing and redistributing power, not just "being invited to the process," and several noted agencies chronically underinvest the time and resources engagement actually requires (p. 12).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Performative versus Authentic Equity Work: An Assessment of Current Practices in Transportation Planning</t>
+          <t>Assessing equity in infrastructure investment distribution among U.S. cities</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>McCullough et al.</t>
+          <t>Chen et al.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Transportation Research Record, 2678(5), 884-903</t>
+          <t>Cities, 162, 105898</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1177/03611981231193409</t>
+          <t>https://doi.org/10.1016/j.cities.2025.105898</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Performative vs authentic equity</t>
+          <t>Infrastructure investment distribution</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Interviews with 28 Black and people of color transportation professionals in California distinguish performative equity work, which privileges dominant groups' comfort and produces only superficial change, from authentic equity work, which redistributes decision making power and produces measurable change for historically oppressed communities.</t>
+          <t>A deep learning analysis of infrastructure expenditure and social vulnerability across 394 US municipalities finds infrastructure investment inequality increased from 2010 to 2019 in nearly every sector, and that shifting from population based to equity centered funding allocation would measurably reduce socioeconomic vulnerability.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Performative equity work: actions or rhetoric that claim to address equity without materially changing outcomes or power. Authentic equity work: sustained redistribution of funding, time, and decision making power to affected communities. Arrested mobility: policing practices that apprehend or harm Black people simply for moving through public space.</t>
+          <t>Social Vulnerability Index: a CDC composite measure of socioeconomic disadvantage used to track which municipalities are underserved. Equality centered versus equity centered allocation: distributing infrastructure funds evenly per capita versus targeting funds toward the most vulnerable municipalities.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Twenty eight California transportation professionals who identify as Black, Indigenous, or people of color, centered through their own workplace and policy experiences.</t>
+          <t>The perspective of planners and policymakers modeling municipal level spending data; no residents of the municipalities studied are directly consulted.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Relational trust and equitable access: performative equity work keeps decision making power concentrated among historically dominant, often white leadership, even while claiming to value equity, leaving communities without real control over resources.</t>
+          <t>Relational trust and flexibility for variable need: the model treats equity as a quantitative allocation formula, and the authors themselves note it lacks the community engagement needed to capture residents' actual perspectives and concerns.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Supports both halves of the claim. It documents uneven distribution of power and voice among transportation professionals of color within the field itself, and argues that infrastructure and funding decisions made without genuinely redistributing power to communities, not just consulting them, reproduce the same exclusion regardless of stated equity commitments.</t>
+          <t>Supports the unevenly distributed half directly, quantifying growing infrastructure investment inequality across a decade and showing which municipalities are shortchanged. It is a thinner fit for the participation half: the framework is data driven and top down, and the authors themselves flag the need to pair it with community engagement to make decisions genuinely equitable.</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>The study is limited to California and did not achieve representation from Indigenous or tribal transportation professionals despite specific recruitment efforts, limiting the framework's tested scope.</t>
+          <t>The model treats infrastructure categories broadly without distinguishing transportation modes, relies on a black box machine learning approach whose internal relationships are hard to interpret, and by the authors' own account still needs community-driven qualitative input.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>"Many communities know the solutions to the challenges they face" (p. 12).</t>
+          <t>"fosters community engagement and ownership, leading to further improvements in the equitable decision-making process" (p. 11).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>This paper reframes community participation as insufficient unless paired with actual redistribution of power and resources, showing that even self identified equity conscious agencies can produce only performative change. It supports the section's exclusion claim by locating the same power imbalance inside the transportation profession itself, not only in public facing planning processes.</t>
+          <t>This paper offers strong quantitative evidence that infrastructure investment inequality has been widening and that equity centered allocation would help close it, reinforcing the section's uneven distribution claim. It is honest about its own limits, though: as a purely data driven model, it cannot substitute for the community engagement the section argues infrastructure decisions actually require.</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>None described. This is a quantitative, GIS and social vulnerability index driven framework for evaluating infrastructure investment allocation across cities. It cites other scholars (Bailey and Grossardt 2010, Karner and Marcantonio 2018) approvingly for the importance of community engagement and recommends surveys and interviews as future work, but the authors' own methodology involves no interaction with residents or communities.</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Assessing equity in infrastructure investment distribution among U.S. cities</t>
+          <t>Race, Space, and Struggles for Mobility: Transportation Impacts on African Americans in Oakland and the East Bay</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chen et al.</t>
+          <t>Golub et al.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Cities, 162, 105898</t>
+          <t>Urban Geography</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.cities.2025.105898</t>
+          <t>https://doi.org/10.1080/02723638.2013.778598</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Infrastructure investment distribution</t>
+          <t>Racialized transit disinvestment</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>A deep learning analysis of infrastructure expenditure and social vulnerability across 394 US municipalities finds infrastructure investment inequality increased from 2010 to 2019 in nearly every sector, and that shifting from population based to equity centered funding allocation would measurably reduce socioeconomic vulnerability.</t>
+          <t>A 2005 civil rights lawsuit against the Bay Area's Metropolitan Transportation Commission reveals that race neutral regional transit funding, favoring suburban rail expansion over Oakland bus service, reproduced a racialized geography built by decades of earlier overt housing and employment discrimination.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index: a CDC composite measure of socioeconomic disadvantage used to track which municipalities are underserved. Equality centered versus equity centered allocation: distributing infrastructure funds evenly per capita versus targeting funds toward the most vulnerable municipalities.</t>
+          <t>Environmental racism framework: analyzes how transportation decisions distribute benefits and burdens along racial lines through exclusion from planning, localized burdens, and unequal mobility access. White noose: the ring of suburban opportunity surrounding racially segregated urban cores. Racism without racists: discriminatory outcomes produced by facially neutral technical criteria layered onto an already segregated geography.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>The perspective of planners and policymakers modeling municipal level spending data; no residents of the municipalities studied are directly consulted.</t>
+          <t>African American bus riders in Oakland and the East Bay, and the civil rights plaintiffs who challenged MTC's funding decisions in Darensburg v. MTC.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Relational trust and flexibility for variable need: the model treats equity as a quantitative allocation formula, and the authors themselves note it lacks the community engagement needed to capture residents' actual perspectives and concerns.</t>
+          <t>Equitable access: MTC's per rider subsidy favored more affluent, mostly White rail riders over low income bus riders of color, and courts accepted this as a legitimate outcome of neutral technical analysis.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Supports the unevenly distributed half directly, quantifying growing infrastructure investment inequality across a decade and showing which municipalities are shortchanged. It is a thinner fit for the participation half: the framework is data driven and top down, and the authors themselves flag the need to pair it with community engagement to make decisions genuinely equitable.</t>
+          <t>Directly supports both halves of the claim. It documents historically uneven mobility access rooted in de jure discrimination, and shows that even facially race neutral, seemingly participatory regional planning processes reproduced exclusion because minority communities' participation and race equity concerns hit real limits within MTC's decision making.</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>The model treats infrastructure categories broadly without distinguishing transportation modes, relies on a black box machine learning approach whose internal relationships are hard to interpret, and by the authors' own account still needs community-driven qualitative input.</t>
+          <t>The analysis focuses on one metropolitan region and one legal case, and does not evaluate whether newer transit oriented development plans in Priority Development Areas will repeat or interrupt this pattern.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>"fosters community engagement and ownership, leading to further improvements in the equitable decision-making process" (p. 11).</t>
+          <t>"racism without racists" (p. 24).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>This paper offers strong quantitative evidence that infrastructure investment inequality has been widening and that equity centered allocation would help close it, reinforcing the section's uneven distribution claim. It is honest about its own limits, though: as a purely data driven model, it cannot substitute for the community engagement the section argues infrastructure decisions actually require.</t>
+          <t>This paper grounds the section's exclusion claim in a landmark case, showing that race neutral transit funding formulas, layered onto a metropolitan geography built by decades of overt discrimination, can reproduce racial exclusion without any single discriminatory actor. It cautions that formally inclusive planning processes do not guarantee equity when minority participation hits structural limits.</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Historical and legal case analysis, not the authors' own fieldwork, of the San Francisco Bay Area's Metropolitan Transportation Commission (MTC) inviting community advocates onto an advisory committee to review its 1998, 2001, and 2005 regional transportation plan equity analyses after Title VI complaints, plus MTC's separate Partnership Board, an advisory only body of transit agency and government representatives it relied on to justify funding decisions in the later Darensburg civil rights lawsuit. Drawn from Sanchez (2008), Cohen and Hobson (2004), and Public Advocates litigation reports.</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Federal corrective action following Title VI complaints did force MTC to formally invite advocacy organizations onto the advisory committee reviewing its 2001 equity analysis, opening a door that outright refusal to involve advocates in 1998 had kept shut (p. 19).</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Advisory committee members found the process consumed large amounts of activist time on mostly technical discussion while MTC accepted few of their recommendations, leaving one member to call it worse than a waste of time and conclude MTC could now simply say it had consulted the community (p. 20). MTC separately leaned on its advisory only Partnership Board, whose transit agency members felt pressured to acquiesce rather than risk offending a key funding source, to legally justify funding decisions the court still found had a discriminatory impact (p. 21).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Race, Space, and Struggles for Mobility: Transportation Impacts on African Americans in Oakland and the East Bay</t>
+          <t>Implementation science frameworks for active and sustainable transportation interventions with a focus on equity: A scoping review</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Golub et al.</t>
+          <t>McCullogh et al.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Urban Geography</t>
+          <t>Transportation Research Interdisciplinary Perspectives, 38, 102020</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/02723638.2013.778598</t>
+          <t>https://doi.org/10.1016/j.trip.2026.102020</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Racialized transit disinvestment</t>
+          <t>Implementation science, equity</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>A 2005 civil rights lawsuit against the Bay Area's Metropolitan Transportation Commission reveals that race neutral regional transit funding, favoring suburban rail expansion over Oakland bus service, reproduced a racialized geography built by decades of earlier overt housing and employment discrimination.</t>
+          <t>A scoping review of 26 studies finds implementation science frameworks exist for active and sustainable transportation interventions, but only nine explicitly address equity, and community engagement, partnerships, and funding operate as both facilitators and barriers to equitable implementation.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Environmental racism framework: analyzes how transportation decisions distribute benefits and burdens along racial lines through exclusion from planning, localized burdens, and unequal mobility access. White noose: the ring of suburban opportunity surrounding racially segregated urban cores. Racism without racists: discriminatory outcomes produced by facially neutral technical criteria layered onto an already segregated geography.</t>
+          <t>Implementation science: the study of methods and factors that determine whether evidence-based interventions get adopted in practice. Barriers and facilitators: context-specificity, community engagement and participation, partnerships and collaboration, and funding; the same factors can enable or block equitable implementation depending on how they are handled.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>African American bus riders in Oakland and the East Bay, and the civil rights plaintiffs who challenged MTC's funding decisions in Darensburg v. MTC.</t>
+          <t>The perspective of researchers synthesizing published frameworks; the traditionally excluded groups discussed, such as low income residents, ethnic minorities, and women, appear only secondhand through the reviewed studies.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Equitable access: MTC's per rider subsidy favored more affluent, mostly White rail riders over low income bus riders of color, and courts accepted this as a legitimate outcome of neutral technical analysis.</t>
+          <t>Equitable access and flexibility for variable need: most frameworks were built for able bodied road users, and community engagement is often only nominal, with marginalized groups excluded or deterred from participating in complex infrastructure decisions.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Directly supports both halves of the claim. It documents historically uneven mobility access rooted in de jure discrimination, and shows that even facially race neutral, seemingly participatory regional planning processes reproduced exclusion because minority communities' participation and race equity concerns hit real limits within MTC's decision making.</t>
+          <t>Supports the infrastructure without participation reproduces exclusion half, showing that fair representation and participation is necessary for equitable implementation, yet the studies reviewed report groups being actively ignored or deterred by feeling they lack the expertise to engage with complex infrastructure projects, producing unequal power among stakeholders.</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>The analysis focuses on one metropolitan region and one legal case, and does not evaluate whether newer transit oriented development plans in Priority Development Areas will repeat or interrupt this pattern.</t>
+          <t>Only 26 of over 8,500 screened studies met inclusion criteria, and most frameworks that do address equity were developed for Western contexts, which the review itself notes may not transfer to other institutional settings such as China.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>"racism without racists" (p. 24).</t>
+          <t>"excluding some from participating bequeaths unequal powers among stakeholders" (p. 14, McCullogh et al. quoting Al-Sharari, 2022, p. 1316).</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>This paper grounds the section's exclusion claim in a landmark case, showing that race neutral transit funding formulas, layered onto a metropolitan geography built by decades of overt discrimination, can reproduce racial exclusion without any single discriminatory actor. It cautions that formally inclusive planning processes do not guarantee equity when minority participation hits structural limits.</t>
+          <t>This review shows that even when implementation frameworks name community engagement as a success factor, marginalized groups are frequently excluded or deterred from participating, concentrating power among project proponents rather than affected communities. It supports the section's exclusion claim while cautioning that most equity-focused frameworks are Western in origin and may not travel well to other contexts.</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Scoping review, not the authors' own fieldwork. Section 4.2.2 synthesizes community engagement and participation as a named implementation theme across many reviewed active and sustainable transportation studies. Cited processes include Koester et al. (2021) engaging students, caregivers, and community members for a walking school bus program, Adams et al. (2017a) consulting a local community group to select a project route with regular check ins, Bakker et al. (2018) framing citizen participation in cycling policy as both active involvement and education, and Bejarano et al. (2021) crediting community organizations and neighbourhood resident support for program coordination.</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Continuous, ongoing engagement rather than one time consultation was repeatedly credited as a facilitator. Adams and colleagues' regular "checking in" with community program coordinators helped track how an intervention evolved (p. 11), and involving local communities was described across several studies as building ownership, social cohesion, and a sense of community (p. 11).</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Disjointed communication about launch dates and follow up support decreased perceived buy in from parents and residents and worried school leaders in Todorova and colleagues' study (p. 11). Separately, traffic related concerns tied to car oriented planning prevented parent buy in to a school remote drop off program in Bejarano and colleagues' study, showing engagement can fail for reasons outside the process itself (p. 20).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Implementation science frameworks for active and sustainable transportation interventions with a focus on equity: A scoping review</t>
+          <t>Inclusive Mobility: Dismantling transportation injustice at the intersection of race and disability</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>McCullogh et al.</t>
+          <t>Twardzik et al.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Transportation Research Interdisciplinary Perspectives, 38, 102020</t>
+          <t>Disability and Health Journal, 18, 101848</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.trip.2026.102020</t>
+          <t>https://doi.org/10.1016/j.dhjo.2025.101848</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Implementation science, equity</t>
+          <t>Race, disability intersectionality</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>A scoping review of 26 studies finds implementation science frameworks exist for active and sustainable transportation interventions, but only nine explicitly address equity, and community engagement, partnerships, and funding operate as both facilitators and barriers to equitable implementation.</t>
+          <t>Transportation injustice is a product of systemic racism and ableism that compounds for people who are both Black and disabled, since public transit systems were built around an ideal rider who is economically secure, able bodied, and white. Dismantling it requires an intersectional, mobility justice approach centering the leadership of those most impacted.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Implementation science: the study of methods and factors that determine whether evidence-based interventions get adopted in practice. Barriers and facilitators: context-specificity, community engagement and participation, partnerships and collaboration, and funding; the same factors can enable or block equitable implementation depending on how they are handled.</t>
+          <t>Transportation injustice: structural conditions that perpetuate inequities, discrimination, and exclusion based on disability, race, class, gender, and age. Intersectionality: overlapping social identities compound rather than simply add experiences of discrimination. Crip Mobility Justice: a framework prioritizing accessibility, interdependence, and abolition of policing alongside physical infrastructure.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>The perspective of researchers synthesizing published frameworks; the traditionally excluded groups discussed, such as low income residents, ethnic minorities, and women, appear only secondhand through the reviewed studies.</t>
+          <t>Black people and people with disabilities in the United States, especially those holding both identities, whose transportation experiences are argued to be understudied.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Equitable access and flexibility for variable need: most frameworks were built for able bodied road users, and community engagement is often only nominal, with marginalized groups excluded or deterred from participating in complex infrastructure decisions.</t>
+          <t>Equitable access and flexibility for variable need: transit systems designed around an ideal rider formally exclude disabled people and, through redlining and highway placement, disproportionately under-serve Black communities.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Supports the infrastructure without participation reproduces exclusion half, showing that fair representation and participation is necessary for equitable implementation, yet the studies reviewed report groups being actively ignored or deterred by feeling they lack the expertise to engage with complex infrastructure projects, producing unequal power among stakeholders.</t>
+          <t>Directly supports both halves of the claim. It traces mobility exclusion to slavery, redlining, and highway construction, and gives a concrete contemporary case: Maryland canceling the Black-serving Red Line to fund the whiter Purple Line without seeking input from Baltimore residents or community groups.</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Only 26 of over 8,500 screened studies met inclusion criteria, and most frameworks that do address equity were developed for Western contexts, which the review itself notes may not transfer to other institutional settings such as China.</t>
-        </is>
-      </c>
-      <c r="M13" s="1" t="inlineStr">
-        <is>
-          <t>"excluding some from participating bequeaths unequal powers among stakeholders" (p. 14, McCullogh et al. quoting Al-Sharari, 2022, p. 1316).</t>
+          <t>The authors note a dearth of evidence at the intersection of race and disability specifically, since disability studies tend to exclude race and race studies tend to omit disability, leaving this population understudied.</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>"The administration did not seek input from the Department of Transportation, Baltimore citizens, or community groups on this decision" (p. 2).</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>This review shows that even when implementation frameworks name community engagement as a success factor, marginalized groups are frequently excluded or deterred from participating, concentrating power among project proponents rather than affected communities. It supports the section's exclusion claim while cautioning that most equity-focused frameworks are Western in origin and may not travel well to other contexts.</t>
+          <t>This paper grounds the section's claim in a concrete recent case, Maryland defunding the Black-serving Red Line for the whiter Purple Line without community input, while tracing the same exclusionary pattern back through redlining and highway construction. It argues dismantling this requires sharing decision-making power with Black and disabled communities as leaders, not only building accessible infrastructure.</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>None described. This is a policy commentary drawing on historical and secondary sources, not the authors' own fieldwork. It recommends, as a forward looking policy prescription, involving potential users at all stages of the transportation lifecycle including design and advisory boards, but names no specific process, participants, or outcome.</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Inclusive Mobility: Dismantling transportation injustice at the intersection of race and disability</t>
+          <t>Inclusive and Accessible Transportation for All: Strategies for Integrating Equity in Transportation Research</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Twardzik et al.</t>
+          <t>Johnson et al.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1409,64 +1636,79 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Disability and Health Journal, 18, 101848</t>
+          <t>Logistics, 9(2), 72</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.dhjo.2025.101848</t>
+          <t>https://doi.org/10.3390/logistics9020072</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Race, disability intersectionality</t>
+          <t>Equity measurement frameworks</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Transportation injustice is a product of systemic racism and ableism that compounds for people who are both Black and disabled, since public transit systems were built around an ideal rider who is economically secure, able bodied, and white. Dismantling it requires an intersectional, mobility justice approach centering the leadership of those most impacted.</t>
+          <t>A literature review of transportation equity research finds that horizontal equity, equal treatment of similar groups, and vertical equity, prioritizing disadvantaged populations, remain inconsistently defined and measured across studies, and that clearer frameworks, better data, and more inclusive decision-making are needed to close this gap.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Transportation injustice: structural conditions that perpetuate inequities, discrimination, and exclusion based on disability, race, class, gender, and age. Intersectionality: overlapping social identities compound rather than simply add experiences of discrimination. Crip Mobility Justice: a framework prioritizing accessibility, interdependence, and abolition of policing alongside physical infrastructure.</t>
+          <t>Horizontal equity: equal treatment of individuals or groups with similar needs. Vertical equity: allocating resources based on differing needs, prioritizing disadvantaged groups. Accessibility indices and affordability metrics: quantitative tools used alongside community engagement approaches to assess whether a transportation system is equitable.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Black people and people with disabilities in the United States, especially those holding both identities, whose transportation experiences are argued to be understudied.</t>
+          <t>The perspective of transportation researchers synthesizing published equity literature and metrics, rather than the residents these metrics are meant to serve.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Equitable access and flexibility for variable need: transit systems designed around an ideal rider formally exclude disabled people and, through redlining and highway placement, disproportionately under-serve Black communities.</t>
+          <t>Relational trust: the review treats community engagement as one measurement tool among several, alongside accessibility indices, rather than as the mechanism through which communities hold real decision-making power.</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Directly supports both halves of the claim. It traces mobility exclusion to slavery, redlining, and highway construction, and gives a concrete contemporary case: Maryland canceling the Black-serving Red Line to fund the whiter Purple Line without seeking input from Baltimore residents or community groups.</t>
+          <t>A thinner fit than most sources in this section: this is a broad measurement focused literature review rather than a case study of participation or exclusion. It touches the unevenly distributed half by cataloging accessibility and affordability metrics, and gestures at the participation half only in its closing recommendation for more inclusive, community-driven decision-making.</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>The authors note a dearth of evidence at the intersection of race and disability specifically, since disability studies tend to exclude race and race studies tend to omit disability, leaving this population understudied.</t>
+          <t>The review draws on a single geographic context, and the authors acknowledge that transportation inequities and appropriate remedies vary substantially by density and region, limiting how directly its recommendations transfer.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>"The administration did not seek input from the Department of Transportation, Baltimore citizens, or community groups on this decision" (p. 2).</t>
+          <t>"Inclusive decision-making processes that involve underrepresented communities will ensure that their voices are considered" (p. 25).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>This paper grounds the section's claim in a concrete recent case, Maryland defunding the Black-serving Red Line for the whiter Purple Line without community input, while tracing the same exclusionary pattern back through redlining and highway construction. It argues dismantling this requires sharing decision-making power with Black and disabled communities as leaders, not only building accessible infrastructure.</t>
+          <t>This review is useful mainly as a map of how transportation equity gets measured, horizontal versus vertical equity, accessibility indices, affordability metrics, rather than as evidence of participation's role in preventing exclusion. It is included with that caveat: its value here is cataloging the measurement landscape the section's case studies push back against.</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>None described. This is a review of quantitative and analytical equity assessment tools (cost-benefit analysis, multi-criteria decision-making, Lorenz curves, GIS clustering, accessibility indices), not the authors' own fieldwork. Community engagement is named only in passing, alongside affordability metrics, as one category of approach other studies use, with no specific process, participants, or outcome described.</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Inclusive and Accessible Transportation for All: Strategies for Integrating Equity in Transportation Research</t>
+          <t>Is the medium the message? Exploring the intersection of social media and collective action in the San Jose Bike Party</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1476,722 +1718,872 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Logistics, 9(2), 72</t>
+          <t>Annals of Leisure Research, 27(4), 543-559</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/logistics9020072</t>
+          <t>https://doi.org/10.1080/11745398.2022.2156363</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Equity measurement frameworks</t>
+          <t>Bike activism, social media</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>A literature review of transportation equity research finds that horizontal equity, equal treatment of similar groups, and vertical equity, prioritizing disadvantaged populations, remain inconsistently defined and measured across studies, and that clearer frameworks, better data, and more inclusive decision-making are needed to close this gap.</t>
+          <t>Interviews and field observations with the San Jose Bike Party, a monthly mass cycling ride organized via social media, find participants hold contested and often depoliticized understandings of the event as collective action, complicating claims that social media organizing democratizes civic participation.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Horizontal equity: equal treatment of individuals or groups with similar needs. Vertical equity: allocating resources based on differing needs, prioritizing disadvantaged groups. Accessibility indices and affordability metrics: quantitative tools used alongside community engagement approaches to assess whether a transportation system is equitable.</t>
+          <t>Prefigurative politics: enacting the change one advocates for through the form of the collective action itself, here temporarily claiming road space for cyclists. Virtual activism: activism organized through social media platforms, of contested lasting impact. Democratic divide: unequal ability to participate in a movement based on access to its digital organizing platforms.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>The perspective of transportation researchers synthesizing published equity literature and metrics, rather than the residents these metrics are meant to serve.</t>
+          <t>San Jose Bike Party organizers and riders, interviewed and observed by researchers who themselves participated in the rides.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Relational trust: the review treats community engagement as one measurement tool among several, alongside accessibility indices, rather than as the mechanism through which communities hold real decision-making power.</t>
+          <t>Equitable access: the ride route is posted exclusively on electronic platforms, so participation depends on social media access and literacy, and many riders described unclear or purely recreational motives rather than a shared advocacy purpose.</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>A thinner fit than most sources in this section: this is a broad measurement focused literature review rather than a case study of participation or exclusion. It touches the unevenly distributed half by cataloging accessibility and affordability metrics, and gestures at the participation half only in its closing recommendation for more inclusive, community-driven decision-making.</t>
+          <t>A thinner fit for this section's specific claim: the study centers a recreational social movement rather than an infrastructure planning process, and most participants did not describe SJBP as political. Its relevance is indirect, since the authors connect it to broader questions of equity, access, and inclusion in cycling infrastructure advocacy, without empirically testing that connection here.</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>The review draws on a single geographic context, and the authors acknowledge that transportation inequities and appropriate remedies vary substantially by density and region, limiting how directly its recommendations transfer.</t>
+          <t>The paper does not analyze whether SJBP has produced any actual change in cycling infrastructure, planning, or policy, and the authors explicitly flag this as a needed direction for future research.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>"Inclusive decision-making processes that involve underrepresented communities will ensure that their voices are considered" (p. 25).</t>
+          <t>"the ride route, which is exclusively posted on electronic platforms" (p. 10).</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>This review is useful mainly as a map of how transportation equity gets measured, horizontal versus vertical equity, accessibility indices, affordability metrics, rather than as evidence of participation's role in preventing exclusion. It is included with that caveat: its value here is cataloging the measurement landscape the section's case studies push back against.</t>
+          <t>This paper is included as a boundary case rather than a direct source: it studies grassroots cycling collective action, not infrastructure planning, and finds participants' political motives were often muddled rather than clear. Its value to the section is the authors' own gesture toward equity focused cycling infrastructure advocacy, a connection this study raises but does not test.</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>The authors' own method is qualitative fieldwork on the San Jose Bike Party (SJBP): semi-structured one on one interviews, about one to 1.5 hours, and two focus groups of five and six participants, with 21 riders total, plus researchers riding along as participant observers and conducting moving interviews mid ride, with field notes and video. This studies a grassroots social movement's own culture, not an agency led consultation of residents. Substantively, SJBP itself pre plans rides and shares information with members beforehand, unlike the structureless Critical Mass rides it grew out of.</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Riding along as participant observers, not just interviewing afterward, let researchers conduct interviews on the move and capture the event's atmosphere directly, yielding thick descriptions a seated interview alone would have missed (p. 8). The hour plus, semi structured format gave riders room to describe unclear or personal motives in their own terms rather than fitting a predetermined political frame (p. 9).</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>This is a study of a self organizing bike collective's own culture, not an evaluation of an agency's consultation process, so it offers no direct evidence on institutional participation succeeding or failing. The closest finding is methodological: participants themselves were often unclear or contradictory about what Bike Party represents, so the interviews surfaced ambiguity in collective purpose rather than a clean account of shared goals (p. 9).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Is the medium the message? Exploring the intersection of social media and collective action in the San Jose Bike Party</t>
+          <t>Achieving transportation equity: Meaningful public involvement to meet the needs of underserved communities</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Johnson et al.</t>
+          <t>Karner et al.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Annals of Leisure Research, 27(4), 543-559</t>
+          <t>Public Works Management &amp; Policy</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/11745398.2022.2156363</t>
+          <t>https://doi.org/10.1177/1087724X17738792</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bike activism, social media</t>
+          <t>Meaningful public involvement model</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Interviews and field observations with the San Jose Bike Party, a monthly mass cycling ride organized via social media, find participants hold contested and often depoliticized understandings of the event as collective action, complicating claims that social media organizing democratizes civic participation.</t>
+          <t>Despite civil rights and environmental justice mandates, transportation planning continues to disproportionately burden low income and minority communities because public involvement processes rarely give residents real influence over decisions. The paper proposes a three step model: community led identification of needs, dedicated funding to meet them, and community derived metrics to track progress.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Prefigurative politics: enacting the change one advocates for through the form of the collective action itself, here temporarily claiming road space for cyclists. Virtual activism: activism organized through social media platforms, of contested lasting impact. Democratic divide: unequal ability to participate in a movement based on access to its digital organizing platforms.</t>
+          <t>Just process versus just outcomes: meaningful involvement of historically burdened communities versus fair distribution of benefits and burdens. Priority unmet needs: a model of equity grounded in what communities themselves identify as needed, not abstract quantitative equity analysis. Participatory budgeting: dedicating funds directly to needs identified through community deliberation.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>San Jose Bike Party organizers and riders, interviewed and observed by researchers who themselves participated in the rides.</t>
+          <t>Low income and minority residents of the San Francisco Bay Area and California communities affected by MPO transportation planning decisions.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Equitable access: the ride route is posted exclusively on electronic platforms, so participation depends on social media access and literacy, and many riders described unclear or purely recreational motives rather than a shared advocacy purpose.</t>
+          <t>Relational trust and equitable access: standard MPO public involvement and quantitative equity analyses omit race and rely on distant forecasts, so they rarely translate community input into funded action.</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>A thinner fit for this section's specific claim: the study centers a recreational social movement rather than an infrastructure planning process, and most participants did not describe SJBP as political. Its relevance is indirect, since the authors connect it to broader questions of equity, access, and inclusion in cycling infrastructure advocacy, without empirically testing that connection here.</t>
+          <t>Directly supports the infrastructure without participation reproduces exclusion half. It argues traditional public involvement is a near absence of meaningful engagement, and proposes a concrete alternative in which community identified needs receive dedicated funding, directly linking genuine participation to just infrastructure outcomes rather than treating them as separate.</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>The paper does not analyze whether SJBP has produced any actual change in cycling infrastructure, planning, or policy, and the authors explicitly flag this as a needed direction for future research.</t>
+          <t>The model's case studies are drawn from California, a state with an unusually strong environmental justice advocacy history and well resourced community based organizations, which the authors note may limit transferability elsewhere.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>"the ride route, which is exclusively posted on electronic platforms" (p. 10).</t>
+          <t>"a near-absence of meaningful public involvement through which affected residents can influence and shape decisions" (p. 2 of the author preprint).</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>This paper is included as a boundary case rather than a direct source: it studies grassroots cycling collective action, not infrastructure planning, and finds participants' political motives were often muddled rather than clear. Its value to the section is the authors' own gesture toward equity focused cycling infrastructure advocacy, a connection this study raises but does not test.</t>
+          <t>This paper offers the section's participatory alternative in concrete, actionable form: community identified needs tied to dedicated funding and community derived metrics, rather than public involvement as a box checking exercise. It reinforces that meaningful participation and just outcomes are not separable goals, directly grounding the exclusion half of the claim in an implementable model.</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Literature review plus two California case studies, not the authors' own fieldwork. CARB's SB 535 guidance process gathered community defined priority needs from community based organizations via public meetings and online input to shape statewide cap and trade investment criteria. Separately, the 6 Wins for Social Equity coalition, over 20 Bay Area social, economic and environmental justice groups, ran its own community driven process entirely outside MTC's official channels to build an alternative regional transportation and land use scenario, Equity Environment and Jobs, later formally analyzed by the agency alongside its own alternatives.</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Advocates called CARB's engagement well executed and responsive during guideline development, and the process surfaced community defined needs, public health, safety, economic, and environmental, that diverged sharply from agencies' usual cost effectiveness metrics (p. 9-10). The 6 Wins coalition's self built EEJ scenario outperformed MTC's own alternatives on displacement risk, rent savings, and pollution, and the agency officially designated it the environmentally superior alternative among five scenarios (p. 12).</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Community groups flagged that CARB's later individual project selection relied on posting information mainly online, creating a digital divide, and that no comprehensive evaluation of SB 535 public involvement has been conducted (p. 10-11). Despite the EEJ scenario's superior performance, MTC adopted only some of its amendments rather than the community's plan itself, so authorship of a winning alternative did not translate into full authority over the final decision (p. 12).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Achieving transportation equity: Meaningful public involvement to meet the needs of underserved communities</t>
+          <t>Limitations of Technical Approaches to Transport Planning Practice in Two Cases: Social Issues as a Critical Component of Urban Projects</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Karner et al.</t>
+          <t>Mottee et al.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Public Works Management &amp; Policy</t>
+          <t>Planning Theory &amp; Practice, 21(1), 39-57</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1177/1087724X17738792</t>
+          <t>https://doi.org/10.1080/14649357.2019.1696980</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Meaningful public involvement model</t>
+          <t>Technical planning, social impacts</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Despite civil rights and environmental justice mandates, transportation planning continues to disproportionately burden low income and minority communities because public involvement processes rarely give residents real influence over decisions. The paper proposes a three step model: community led identification of needs, dedicated funding to meet them, and community derived metrics to track progress.</t>
+          <t>Case studies of Amsterdam's North-South Metro line and Sydney's Parramatta Rail Link find that technical, model driven transport planning consistently overlooks social impacts, contributing to lost social licence, poor communication, and inadequate protection of affected communities. Social Impact Assessment, applied early, offers a path to better integrate social issues into megaproject planning.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Just process versus just outcomes: meaningful involvement of historically burdened communities versus fair distribution of benefits and burdens. Priority unmet needs: a model of equity grounded in what communities themselves identify as needed, not abstract quantitative equity analysis. Participatory budgeting: dedicating funds directly to needs identified through community deliberation.</t>
+          <t>Social Impact Assessment: a framework for anticipating and managing how projects change people's lives, distinct from purely economic or engineering impact models. Social licence to operate: a community's ongoing acceptance of a project, lost through poor communication and unmet commitments. Predict and provide: a quantitative, model driven planning approach criticized for ignoring wider social context.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Low income and minority residents of the San Francisco Bay Area and California communities affected by MPO transportation planning decisions.</t>
+          <t>Communities affected by two rail megaprojects, and infrastructure impact assessment practitioners interviewed about planning practice in Amsterdam and Sydney.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Relational trust and equitable access: standard MPO public involvement and quantitative equity analyses omit race and rely on distant forecasts, so they rarely translate community input into funded action.</t>
+          <t>Relational trust and flexibility for variable need: technical, model driven planning treats social impacts as secondary to economic and engineering considerations, so affected communities' actual needs go unconsidered until consultation happens too late to shape decisions.</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Directly supports the infrastructure without participation reproduces exclusion half. It argues traditional public involvement is a near absence of meaningful engagement, and proposes a concrete alternative in which community identified needs receive dedicated funding, directly linking genuine participation to just infrastructure outcomes rather than treating them as separate.</t>
+          <t>Directly supports the infrastructure without participation reproduces exclusion half. Both rail megaprojects show that public consultation occurring late in the project lifecycle fails to transfer community input into how social impacts get assessed and managed, diluting the public's capacity to meaningfully shape infrastructure that affects them.</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>The model's case studies are drawn from California, a state with an unusually strong environmental justice advocacy history and well resourced community based organizations, which the authors note may limit transferability elsewhere.</t>
-        </is>
-      </c>
-      <c r="M17" s="1" t="inlineStr">
-        <is>
-          <t>"a near-absence of meaningful public involvement through which affected residents can influence and shape decisions" (p. 2 of the author preprint).</t>
+          <t>The study examines only two rail megaprojects in wealthy, high capacity planning contexts, Amsterdam and Sydney, so it may understate the barriers to adopting Social Impact Assessment in lower resourced planning systems.</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>"dilute the capacity of the public to contribute meaningfully to transport planning" (p. 15).</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>This paper offers the section's participatory alternative in concrete, actionable form: community identified needs tied to dedicated funding and community derived metrics, rather than public involvement as a box checking exercise. It reinforces that meaningful participation and just outcomes are not separable goals, directly grounding the exclusion half of the claim in an implementable model.</t>
+          <t>This paper shows, through two concrete megaproject cases, that consultation without a mechanism to feed into actual project design amounts to participation in name only. It reinforces the exclusion claim by tracing the same failure, technical dominance sidelining community input, across two different high income cities, and proposes Social Impact Assessment as a structural fix rather than a procedural add on.</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>The authors' own method is roughly 30 semi-structured interviews with project stakeholders, government officials, consultants, aldermen, and citizens' representatives, across two infrastructure megaprojects, Sydney's Action for Transport plan and Amsterdam's North South metro line (NZL), plus a focus group with five impact assessment experts, analyzed thematically. The paper compares each country's formal consultation requirements within environmental and social impact assessment and land use planning against how much influence residents actually had over the final design.</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Focus group experts and the authors agree that engaging communities early, during strategic and pre-feasibility assessment before the project concept is fixed, offers the greatest potential to build trust and genuinely incorporate alternatives that benefit local communities (p. 11). When impact assessment is treated as big picture thinking before action rather than a narrow legal box to check, practitioners say its role in shaping decisions can be substantial rather than just validating a plan already chosen (p. 11).</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>In Amsterdam's formally required citizen consultation, the plan was already finalized before residents were asked for input, and suggested changes were rejected as already decided, leading one citizens' representative to ask, "So why then do you ask us?" (p. 10). The authors read this as producing underlying public mistrust in the municipality and a lack of real influence over decisions, since formal consultation carried no requirement to actually modify the project.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Limitations of Technical Approaches to Transport Planning Practice in Two Cases: Social Issues as a Critical Component of Urban Projects</t>
+          <t>Lived expertise of the structurally disadvantaged: towards a more just participatory transport planning process</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mottee et al.</t>
+          <t>Klaever et al.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Planning Theory &amp; Practice, 21(1), 39-57</t>
+          <t>Mobilities, 20(3), 555-572</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/14649357.2019.1696980</t>
+          <t>https://doi.org/10.1080/17450101.2024.2426554</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Technical planning, social impacts</t>
+          <t>Lived expertise, non-participation</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Case studies of Amsterdam's North-South Metro line and Sydney's Parramatta Rail Link find that technical, model driven transport planning consistently overlooks social impacts, contributing to lost social licence, poor communication, and inadequate protection of affected communities. Social Impact Assessment, applied early, offers a path to better integrate social issues into megaproject planning.</t>
+          <t>Focus groups with mobility disabled people and low income women in Berlin's Graefekiez neighborhood find that non-participation in street space reallocation planning stems from feeling excluded and ignored by prior participatory processes, while a purpose built, transdisciplinary research format better reflected residents' lived expertise.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Social Impact Assessment: a framework for anticipating and managing how projects change people's lives, distinct from purely economic or engineering impact models. Social licence to operate: a community's ongoing acceptance of a project, lost through poor communication and unmet commitments. Predict and provide: a quantitative, model driven planning approach criticized for ignoring wider social context.</t>
+          <t>Lived expertise: the practical, embodied knowledge structurally disadvantaged people hold about their own mobility needs, distinct from technical planning expertise. Invited versus claimed spaces: participation opportunities designed by authorities versus spaces residents create themselves. Negative political self-efficacy: the learned sense that speaking up in official participatory venues will not lead anywhere.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Communities affected by two rail megaprojects, and infrastructure impact assessment practitioners interviewed about planning practice in Amsterdam and Sydney.</t>
+          <t>Mobility disabled residents and women from a low socioeconomic status neighborhood in Berlin, recruited specifically for their structurally disadvantaged position.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Relational trust and flexibility for variable need: technical, model driven planning treats social impacts as secondary to economic and engineering considerations, so affected communities' actual needs go unconsidered until consultation happens too late to shape decisions.</t>
+          <t>Relational trust and equitable access: repeated negative experiences in official participatory venues, including public humiliation by a mayor, taught disadvantaged residents their input would not be acted on, so many stopped participating altogether.</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Directly supports the infrastructure without participation reproduces exclusion half. Both rail megaprojects show that public consultation occurring late in the project lifecycle fails to transfer community input into how social impacts get assessed and managed, diluting the public's capacity to meaningfully shape infrastructure that affects them.</t>
+          <t>Directly supports the infrastructure without participation reproduces exclusion half. It shows concretely how invited participatory spaces, meant to democratize a car space reallocation project, actively discouraged the structurally disadvantaged residents they claimed to include, reproducing the same exclusion the project intended to fix.</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>The study examines only two rail megaprojects in wealthy, high capacity planning contexts, Amsterdam and Sydney, so it may understate the barriers to adopting Social Impact Assessment in lower resourced planning systems.</t>
+          <t>The case study is a single Berlin neighborhood under a specific green party led local government, and the authors note it is not perfectly generalizable to other transport planning contexts.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>"dilute the capacity of the public to contribute meaningfully to transport planning" (p. 15).</t>
+          <t>"I've been talking to and against walls for years" (p. 11).</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>This paper shows, through two concrete megaproject cases, that consultation without a mechanism to feed into actual project design amounts to participation in name only. It reinforces the exclusion claim by tracing the same failure, technical dominance sidelining community input, across two different high income cities, and proposes Social Impact Assessment as a structural fix rather than a procedural add on.</t>
+          <t>This paper offers a vivid, first person account of how official participation processes can actively produce the disengagement they are meant to prevent, directly reinforcing the claim that infrastructure decisions without genuine participation reproduce exclusion. It also models an alternative, a co-designed research format residents experienced as more welcoming and reflective of their lived expertise.</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>The authors' own method is three rounds of two hour focus groups, August to December 2023, with mobility disabled residents and women from a social housing estate in Berlin's Graefekiez, recruited via flyers, social media, and visits to existing community spaces like a weekly women's breakfast, with a 50 euro allowance per session and a final round to collectively discuss findings. This studies the municipality's own Graefekiez street redesign participation program, which used mostly informative and deliberative formats, online surveys, flyers, information events, discussion hours, plus one collaborative parking redesign component, that participant observation found drew a mostly white, middle aged, non disabled crowd.</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Locating focus groups within the neighbourhood and recruiting through trusted existing spaces, like the women's weekly breakfast, reduced physical and social barriers to participating in the authors' own research, though building the women's group still took much more relational work and time than recruiting mobility disabled participants (p. 8). A closing third round that returned findings to participants for collective discussion gave them a direct evaluative role in the research itself (p. 8).</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>In the municipal project itself, delayed information and outreach that skipped disabled and WDS residents' actual communication channels, newspapers and radio for one group, community social media for the other, left people feeling excluded before barriers like time, health, caretaking, or language even came into play (p. 9-10). Participants who had engaged with prior local processes described feeling ignored despite attending, one saying local politics amounted to a "friendly side offer" where "nothing fundamental could be decided" (p. 12).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Lived expertise of the structurally disadvantaged: towards a more just participatory transport planning process</t>
+          <t>Mindsets and actions: Shifts in equitable and sustainable development in U.S. cities</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Klaever et al.</t>
+          <t>Pineo et al.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Mobilities, 20(3), 555-572</t>
+          <t>Urban Studies</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/17450101.2024.2426554</t>
+          <t>https://doi.org/10.1177/00420980261438717</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lived expertise, non-participation</t>
+          <t>Community-led equitable development</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Focus groups with mobility disabled people and low income women in Berlin's Graefekiez neighborhood find that non-participation in street space reallocation planning stems from feeling excluded and ignored by prior participatory processes, while a purpose built, transdisciplinary research format better reflected residents' lived expertise.</t>
+          <t>Interviews with 23 urban development professionals across U.S. cities find a shift toward more explicitly equitable practices, driven less by government initiative than by community-based organizations and residents adopting radical demands for redistributed resources, alongside strategic framing to counter opposition rooted in individualist and racialized cultural mindsets.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Lived expertise: the practical, embodied knowledge structurally disadvantaged people hold about their own mobility needs, distinct from technical planning expertise. Invited versus claimed spaces: participation opportunities designed by authorities versus spaces residents create themselves. Negative political self-efficacy: the learned sense that speaking up in official participatory venues will not lead anywhere.</t>
+          <t>Bottom-up transformation: resident and CBO led initiatives that go beyond procedural inclusion to shift actual resource distribution and power. Bootstraps narrative: a cultural myth of unconstrained individual mobility used to oppose equitable investment. Tactical urbanism: temporary, small scale interventions, such as youth-led road redesigns, used to demonstrate what permanent infrastructure change could look like.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Mobility disabled residents and women from a low socioeconomic status neighborhood in Berlin, recruited specifically for their structurally disadvantaged position.</t>
+          <t>Senior professionals in community development, planning, transportation, and housing across U.S. cities, primarily in local government and nonprofits, describing their own strategies.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Relational trust and equitable access: repeated negative experiences in official participatory venues, including public humiliation by a mayor, taught disadvantaged residents their input would not be acted on, so many stopped participating altogether.</t>
+          <t>Relational trust: city processes and regulations were described as stacked against transformative solutions, so community organizations often had to build parallel, informal coalitions to get equitable projects taken seriously by agencies.</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Directly supports the infrastructure without participation reproduces exclusion half. It shows concretely how invited participatory spaces, meant to democratize a car space reallocation project, actively discouraged the structurally disadvantaged residents they claimed to include, reproducing the same exclusion the project intended to fix.</t>
+          <t>A moderate fit: transportation is one of several urban development domains covered alongside housing and parks, not the primary focus. Where most relevant, a youth-led tactical urbanism project redesigning a high-fatality road, it shows infrastructure change becoming possible only after community-led action pushed a reluctant state agency, illustrating the participation half concretely though not exclusively about mobility.</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>The case study is a single Berlin neighborhood under a specific green party led local government, and the authors note it is not perfectly generalizable to other transport planning contexts.</t>
+          <t>The study relies on 23 interviews with professionals rather than the residents whose neighborhoods are affected, and the authors note a remaining knowledge gap about the cultural mindsets that drive opposition to equitable development in particular places.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>"I've been talking to and against walls for years" (p. 11).</t>
+          <t>"this would not have happened" without the youth-led project, which "sort of elevated it for [the state agency]" and "showed what was possible" (p. 11).</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>This paper offers a vivid, first person account of how official participation processes can actively produce the disengagement they are meant to prevent, directly reinforcing the claim that infrastructure decisions without genuine participation reproduce exclusion. It also models an alternative, a co-designed research format residents experienced as more welcoming and reflective of their lived expertise.</t>
+          <t>This paper is useful mainly for its broader pattern, that community-led pressure, not government initiative, has been the main driver of recent shifts toward equitable urban development, with a concrete mobility example, youth redesigning a dangerous road, illustrating how bottom-up organizing can force infrastructure change agencies would not have pursued alone.</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>The authors' own method is 23 semi-structured interviews with professionals working on equitable, sustainable urban development across U.S. cities, planners, public health officials, chamber of commerce, affordable housing developers, purposively recruited, transcribed, and analyzed with deductive content and narrative analysis. Within their accounts, one concrete case stands out: state funding backed a tactical urbanism group that worked directly with young people to redesign mobility infrastructure on a road with high pedestrian fatalities, starting from a small grant and growing into a significant state funded street redesign.</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>The youth led tactical urbanism project is credited with unlocking state investment that a public health official said "would not have happened" otherwise, because the project "elevated" the issue for the state agency and "showed what was possible" (p. 11). Cross agency steering committees built around specific projects were separately called "one of the most important parts" of similar efforts, fostering collective responsibility across organizations (p. 11).</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Professionals described community and nonprofit led efforts as having to work very hard against city processes and regulations stacked against transformational solutions, with one leader unprepared for how long it took to win city leaders' support for a community land trust meant to prevent displacement (p. 11). Interviewees also described the emotional toll of this work, feeling "raw" after public meetings and spending extra hours to reach outcomes a smoother process would have reached faster (p. 10).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Mindsets and actions: Shifts in equitable and sustainable development in U.S. cities</t>
+          <t>Mobilising equity. Emerging evidence for integrating vulnerable communities</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pineo et al.</t>
+          <t>Di Ruocco</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Urban Studies</t>
+          <t>TeMA - Journal of Land Use, Mobility and Environment, 18(1), 95-112</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1177/00420980261438717</t>
+          <t>http://dx.doi.org/10.6093/1970-9870/10872</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Community-led equitable development</t>
+          <t>ICT mobility, vulnerable groups</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Interviews with 23 urban development professionals across U.S. cities find a shift toward more explicitly equitable practices, driven less by government initiative than by community-based organizations and residents adopting radical demands for redistributed resources, alongside strategic framing to counter opposition rooted in individualist and racialized cultural mindsets.</t>
+          <t>A literature review of global best practices finds that technology driven mobility solutions, such as MaaS platforms and accessible transit systems, improve equity for vulnerable groups only when paired with inclusive land use planning, affordable design, and active community participation, and that rural regions and non-elderly vulnerable groups remain understudied.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Bottom-up transformation: resident and CBO led initiatives that go beyond procedural inclusion to shift actual resource distribution and power. Bootstraps narrative: a cultural myth of unconstrained individual mobility used to oppose equitable investment. Tactical urbanism: temporary, small scale interventions, such as youth-led road redesigns, used to demonstrate what permanent infrastructure change could look like.</t>
+          <t>Mobility-as-a-Service: a digital platform integrating multiple transport modes into one accessible interface. Intersectional mobility vulnerability: overlapping identities such as gender, disability, race, and economic status that compound transportation barriers. Digital divide: unequal access to the devices and connectivity that ICT-based mobility solutions assume users already have.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Senior professionals in community development, planning, transportation, and housing across U.S. cities, primarily in local government and nonprofits, describing their own strategies.</t>
+          <t>The perspective of researchers and policymakers reviewing global case studies; vulnerable groups themselves appear as subjects of the literature rather than direct participants in this review.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Relational trust: city processes and regulations were described as stacked against transformative solutions, so community organizations often had to build parallel, informal coalitions to get equitable projects taken seriously by agencies.</t>
+          <t>Equitable access and flexibility for variable need: most ICT mobility solutions are designed around urban, digitally literate users, leaving rural residents and non-elderly vulnerable groups such as ethnic minorities underexplored and often excluded by design.</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>A moderate fit: transportation is one of several urban development domains covered alongside housing and parks, not the primary focus. Where most relevant, a youth-led tactical urbanism project redesigning a high-fatality road, it shows infrastructure change becoming possible only after community-led action pushed a reluctant state agency, illustrating the participation half concretely though not exclusively about mobility.</t>
+          <t>Supports the unevenly distributed half by cataloging how rural regions and multiple vulnerable groups remain underserved despite smart mobility advancements. It touches the participation half more lightly, noting that engagement must go beyond consultation to active participation in planning, without providing its own case study of that shift.</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>The study relies on 23 interviews with professionals rather than the residents whose neighborhoods are affected, and the authors note a remaining knowledge gap about the cultural mindsets that drive opposition to equitable development in particular places.</t>
-        </is>
-      </c>
-      <c r="M20" s="1" t="inlineStr">
-        <is>
-          <t>"this would not have happened" without the youth-led project, which "sort of elevated it for [the state agency]" and "showed what was possible" (p. 11).</t>
+          <t>The reviewed literature is itself urban centric with limited rural evidence and no longitudinal data, and the paper is a review of secondary sources rather than original fieldwork with vulnerable communities.</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>"engagement must go beyond consultation, requiring active citizen participation in planning" (p. 15).</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>This paper is useful mainly for its broader pattern, that community-led pressure, not government initiative, has been the main driver of recent shifts toward equitable urban development, with a concrete mobility example, youth redesigning a dangerous road, illustrating how bottom-up organizing can force infrastructure change agencies would not have pursued alone.</t>
+          <t>This review is most useful for documenting the uneven distribution half, showing that smart mobility technologies leave rural residents and several vulnerable groups behind despite their promise. Its treatment of participation is brief and aspirational rather than evidenced, so it complements rather than substitutes for the section's more direct participatory case studies.</t>
+        </is>
+      </c>
+      <c r="O20" s="1" t="inlineStr">
+        <is>
+          <t>None described. This paper states plainly that it proceeds 'through a literature review' of emerging research evidence on technology driven mobility solutions for vulnerable groups (TeMA, 2025); it reports no participatory or co-design fieldwork of its own. WARNING: the previous entry described a Berlin Pankow Kiezblock traffic calming co-production case study, with Winsviertel and Gruene Stadt neighborhoods and page cites to p. 4 and p. 6. None of that is in this paper: Pankow, Kiezblock, Winsviertel, and Gruene Stadt all return zero matches, and the only mentions of Berlin are an editorial board affiliation and a one line app example. Those cells were populated from a different source and should not be trusted.</t>
+        </is>
+      </c>
+      <c r="P20" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q20" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mobilising equity. Emerging evidence for integrating vulnerable communities</t>
+          <t>Mobility Injustice by Design</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Di Ruocco</t>
+          <t>Jensen</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>TeMA - Journal of Land Use, Mobility and Environment, 18(1), 95-112</t>
+          <t>Routledge (Changing Mobilities series)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>http://dx.doi.org/10.6093/1970-9870/10872</t>
+          <t>https://doi.org/10.4324/9781003459729</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ICT mobility, vulnerable groups</t>
+          <t>Exclusionary design, mobility justice</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>A literature review of global best practices finds that technology driven mobility solutions, such as MaaS platforms and accessible transit systems, improve equity for vulnerable groups only when paired with inclusive land use planning, affordable design, and active community participation, and that rural regions and non-elderly vulnerable groups remain understudied.</t>
+          <t>Drawing on research into unhoused, disabled, and aging city dwellers, this book argues that mobility injustice is produced by everyday design choices, benches angled to prevent sleeping, high curbs, short pedestrian crossing signals, not only by policy, and asks who the built world is actually designed for.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Mobility-as-a-Service: a digital platform integrating multiple transport modes into one accessible interface. Intersectional mobility vulnerability: overlapping identities such as gender, disability, race, and economic status that compound transportation barriers. Digital divide: unequal access to the devices and connectivity that ICT-based mobility solutions assume users already have.</t>
+          <t>Exclusionary design: material and spatial choices, intentional or not, that curb the mobility of vulnerable groups. Mobility justice: a framework asking who has the right to move, treating autonomous mobility as a fiction sustained by hidden assistance and dependency. Design justice: extending questions of justice to the artifacts and spaces that afford or restrict movement.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>The perspective of researchers and policymakers reviewing global case studies; vulnerable groups themselves appear as subjects of the literature rather than direct participants in this review.</t>
+          <t>Unhoused street sleepers, disabled and impaired people, and aging citizens, examined through the author's Exclusionary Design research project in Copenhagen and beyond.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Equitable access and flexibility for variable need: most ICT mobility solutions are designed around urban, digitally literate users, leaving rural residents and non-elderly vulnerable groups such as ethnic minorities underexplored and often excluded by design.</t>
+          <t>Equitable access and flexibility for variable need: cities are described as built for able bodied, middle class, ordinary citizens, so street furniture and crossing timing are designed around that default and against unhoused, disabled, and aging users.</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Supports the unevenly distributed half by cataloging how rural regions and multiple vulnerable groups remain underserved despite smart mobility advancements. It touches the participation half more lightly, noting that engagement must go beyond consultation to active participation in planning, without providing its own case study of that shift.</t>
+          <t>Directly supports the infrastructure without participation reproduces exclusion half, reframing exclusion as encoded in physical design decisions, hostile benches, curbs, crossing timers, rather than only in planning process or funding. This entry draws only on the book's introductory chapter and bibliography, since the empirical fieldwork chapters were not included in the available preview text.</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>The reviewed literature is itself urban centric with limited rural evidence and no longitudinal data, and the paper is a review of secondary sources rather than original fieldwork with vulnerable communities.</t>
+          <t>Only the introduction and bibliography were available in the extracted preview; the book's empirical chapters on unhoused, disabled, and aging populations, where the fieldwork evidence lives, could not be reviewed here and should be read directly for case level detail.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>"engagement must go beyond consultation, requiring active citizen participation in planning" (p. 15).</t>
+          <t>"Who is the built world built for?" (p. 15, Jensen quoting Hendren, 2020).</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>This review is most useful for documenting the uneven distribution half, showing that smart mobility technologies leave rural residents and several vulnerable groups behind despite their promise. Its treatment of participation is brief and aspirational rather than evidenced, so it complements rather than substitutes for the section's more direct participatory case studies.</t>
+          <t>This book pushes the section's exclusion claim down to the level of material design, arguing that hostile benches, high curbs, and short crossing signals encode exclusion into infrastructure independent of any single planning decision. Only the introductory framing was available here; the book's later chapters presumably supply fieldwork evidence for unhoused, disabled, and aging Copenhageners that would let this claim be checked against lived experience.</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>This PDF is a preview containing only front matter and the introduction chapter of a book, not its empirical chapters. It describes drawing on the "Exclusionary Design, Social Exclusion in Urban Space" research project at Aalborg University (2021 to 2024), which collaborated with Copenhagen's city government and local NGOs and used ethnographic fieldwork and concealed identity interviews with unhoused people to document how street furniture and urban design push them out of public space. The chapters that would detail this fieldwork's methods and outcomes in depth (Chapters 6 to 8) are not included in this preview extract.</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Not discussed in the available preview. The introduction names the collaborative research design and its city government and NGO partnerships but the empirical chapters that would detail which engagement practices succeeded are not part of this extract.</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Not discussed in the available preview, for the same reason: the empirical chapters covering the unhoused, disability, and aging fieldwork are not included in this preview extract.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Mobility Injustice by Design</t>
+          <t>Mobility justice and accessible public transport networks for people with intellectual disability</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Jensen</t>
+          <t>van Holstein et al.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Routledge (Changing Mobilities series)</t>
+          <t>Applied Mobilities</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://doi.org/10.4324/9781003459729</t>
+          <t>https://doi.org/10.1080/23800127.2020.1827557</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Exclusionary design, mobility justice</t>
+          <t>Intellectual disability, network access</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Drawing on research into unhoused, disabled, and aging city dwellers, this book argues that mobility injustice is produced by everyday design choices, benches angled to prevent sleeping, high curbs, short pedestrian crossing signals, not only by policy, and asks who the built world is actually designed for.</t>
+          <t>A focus group of 16 public transport and disability advocacy practitioners in Victoria, Australia finds that Melbourne's privatized, splintered transport network creates cognitive access barriers for people with intellectual disability that no single service provider can fix alone, requiring network wide collaboration and inclusive participation mechanisms.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Exclusionary design: material and spatial choices, intentional or not, that curb the mobility of vulnerable groups. Mobility justice: a framework asking who has the right to move, treating autonomous mobility as a fiction sustained by hidden assistance and dependency. Design justice: extending questions of justice to the artifacts and spaces that afford or restrict movement.</t>
+          <t>Mobility justice: understanding mobility outcomes as generated at the intersection of transport systems and wider social circumstances, here extended to cognitive access. Splintered urbanism: fragmented, privatized transport governance in which competing operators communicate inconsistently. Performative research: a focus group method aimed at prompting collaboration and change, not just recording existing conditions.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Unhoused street sleepers, disabled and impaired people, and aging citizens, examined through the author's Exclusionary Design research project in Copenhagen and beyond.</t>
+          <t>People with intellectual disability as public transport users, represented in the focus group by disability advocacy organizations and a person contributing lived expertise directly.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Equitable access and flexibility for variable need: cities are described as built for able bodied, middle class, ordinary citizens, so street furniture and crossing timing are designed around that default and against unhoused, disabled, and aging users.</t>
+          <t>Equitable access and flexibility for variable need: existing disability access committees typically focus on sensory and physical impairments and often exclude people with intellectual disability, and advocates who do participate are frequently expected to contribute expertise unpaid.</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Directly supports the infrastructure without participation reproduces exclusion half, reframing exclusion as encoded in physical design decisions, hostile benches, curbs, crossing timers, rather than only in planning process or funding. This entry draws only on the book's introductory chapter and bibliography, since the empirical fieldwork chapters were not included in the available preview text.</t>
+          <t>Directly supports the infrastructure without participation reproduces exclusion half. It shows existing participatory mechanisms, access committees and reference groups, systematically underrepresent people with intellectual disability, and argues genuine inclusion requires network wide collaboration across privatized operators plus fair compensation for advocates' expertise.</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Only the introduction and bibliography were available in the extracted preview; the book's empirical chapters on unhoused, disabled, and aging populations, where the fieldwork evidence lives, could not be reviewed here and should be read directly for case level detail.</t>
-        </is>
-      </c>
-      <c r="M22" s="1" t="inlineStr">
-        <is>
-          <t>"Who is the built world built for?" (p. 15, Jensen quoting Hendren, 2020).</t>
+          <t>The study draws on a single one day focus group of practitioners and advocates rather than people with intellectual disability directly, and is limited to one metropolitan transport system in Victoria, Australia.</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>"too often, people with disability are not paid for their expertise" (p. 13).</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>This book pushes the section's exclusion claim down to the level of material design, arguing that hostile benches, high curbs, and short crossing signals encode exclusion into infrastructure independent of any single planning decision. Only the introductory framing was available here; the book's later chapters presumably supply fieldwork evidence for unhoused, disabled, and aging Copenhageners that would let this claim be checked against lived experience.</t>
+          <t>This paper extends the participation half of the claim to an overlooked group, showing that even disability focused participatory structures in transport planning routinely exclude people with intellectual disability, and that meaningful inclusion requires paid, coordinated, network wide effort rather than one-off consultation. It grounds the claim in a concrete account of how existing inclusion mechanisms quietly reproduce exclusion.</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>The authors' own method is a one day, three round focus group in Melbourne with 16 stakeholders: two accessibility officers and a general manager from the three largest bus and rail operators, a regional rail inclusion officer, two Public Transport Victoria representatives, a bus and rail union representative, the Public Transport Users' Association president, a volunteer assistance nonprofit manager, and two disability advocacy representatives, one contributing his own lived experience of intellectual disability. Structured around three questions on current initiatives, barriers and opportunities, and whether inclusive decision making mechanisms exist, with a notetaker and thematic analysis. Designed as performative research meant to also prompt collaboration, not just record findings.</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>The focus group itself sparked real action: a disability advocate present offered on the spot to help recruit people with intellectual disability onto providers' access committees, which the authors call evidence of the method's own performative value (p. 12). Pooling providers' existing disability reference groups and PTAC advice, and sharing information about who is already engaged, was identified as a workable way to build participation capacity across the network (p. 12).</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Providers' existing consumer consultation committees, including the central body PTAC, were found to focus on sensory and physical disability and often exclude people with intellectual disability entirely, despite this population being the paper's own focus (p. 12). Only two of 16 focus group participants represented disability advocacy, and reliance on the same experienced individuals for every reference group across providers was flagged as limiting whose voices actually get heard (p. 12).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Mobility justice and accessible public transport networks for people with intellectual disability</t>
+          <t>North Florida Stakeholder Perspectives: Gaps, Barriers, and Facilitators in the Transportation System</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>van Holstein et al.</t>
+          <t>Jeghers et al.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Applied Mobilities</t>
+          <t>Future Transportation, 4, 1520-1536</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/23800127.2020.1827557</t>
+          <t>https://doi.org/10.3390/futuretransp4040073</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Intellectual disability, network access</t>
+          <t>Stakeholder perspectives, funding gaps</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>A focus group of 16 public transport and disability advocacy practitioners in Victoria, Australia finds that Melbourne's privatized, splintered transport network creates cognitive access barriers for people with intellectual disability that no single service provider can fix alone, requiring network wide collaboration and inclusive participation mechanisms.</t>
+          <t>Interviews with 13 city planners, transportation employees, and state representatives in North Florida find that funding shortfalls and misaligned priorities among stakeholders, not lack of awareness, are the main barriers to equitable transportation for mobility vulnerable populations, and that new technologies are being piloted without yet translating into improved access for those groups.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Mobility justice: understanding mobility outcomes as generated at the intersection of transport systems and wider social circumstances, here extended to cognitive access. Splintered urbanism: fragmented, privatized transport governance in which competing operators communicate inconsistently. Performative research: a focus group method aimed at prompting collaboration and change, not just recording existing conditions.</t>
+          <t>Mobility vulnerable populations: residents below the poverty line, people with disabilities, and older adults with limited transportation options. SWOT framework: strengths, weaknesses, opportunities, and threats used to structure stakeholders' assessment of the transportation system. Smart Cities Collaborative: a multi city initiative piloting technologies like autonomous rideshare intended to reduce transportation disparities.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>People with intellectual disability as public transport users, represented in the focus group by disability advocacy organizations and a person contributing lived expertise directly.</t>
+          <t>Transportation professionals, city planners, agency employees, and state representatives, rather than the mobility vulnerable residents whose needs are being discussed.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Equitable access and flexibility for variable need: existing disability access committees typically focus on sensory and physical impairments and often exclude people with intellectual disability, and advocates who do participate are frequently expected to contribute expertise unpaid.</t>
+          <t>Equitable access: one participant described a higher minority area of Gainesville as still hurting because state and city funding priorities do not match that community's needs, reflecting a persistent misalignment between resource allocation and who actually needs it.</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Directly supports the infrastructure without participation reproduces exclusion half. It shows existing participatory mechanisms, access committees and reference groups, systematically underrepresent people with intellectual disability, and argues genuine inclusion requires network wide collaboration across privatized operators plus fair compensation for advocates' expertise.</t>
+          <t>A moderate fit for the unevenly distributed half, since it documents professionals' own acknowledgment that funding and priorities are misaligned with mobility vulnerable and minority populations. It is thinner on the participation half: the study centers professional perspectives rather than community members, and stakeholders admit new technologies have not yet been communicated to the users they are meant to serve.</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>The study draws on a single one day focus group of practitioners and advocates rather than people with intellectual disability directly, and is limited to one metropolitan transport system in Victoria, Australia.</t>
+          <t>The study interviewed only 13 stakeholders, all transportation professionals, and the authors note responses may be shaped by participants' professional roles or concern about their employers rather than by mobility vulnerable residents' own perspectives.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>"too often, people with disability are not paid for their expertise" (p. 13).</t>
+          <t>"Politicians come and go. They have priorities, and they do not always match [the priorities of multiple stakeholders]" (p. 7).</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>This paper extends the participation half of the claim to an overlooked group, showing that even disability focused participatory structures in transport planning routinely exclude people with intellectual disability, and that meaningful inclusion requires paid, coordinated, network wide effort rather than one-off consultation. It grounds the claim in a concrete account of how existing inclusion mechanisms quietly reproduce exclusion.</t>
+          <t>This paper documents uneven distribution from the professional side, showing transportation officials themselves recognize that funding and political priorities leave some communities, especially higher minority areas, underserved. It is a weaker source for the participation half, since it centers professionals' self-assessment rather than mobility vulnerable residents' direct accounts of exclusion.</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>None described as a resident facing process. The authors' own method is 13 semi-structured interviews with transportation professionals, city planners, transportation agency employees, industry stakeholders, and state representatives, recruited through purposive and snowball sampling, not with community members or riders directly. Findings center on professional goal alignment and public education and outreach campaigns, such as hands-on training and safety resource websites, rather than any process that consulted community members in shaping decisions.</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>North Florida Stakeholder Perspectives: Gaps, Barriers, and Facilitators in the Transportation System</t>
+          <t>Quantification of latent travel demand across age groups with a focus on older adults: a theoretical framework with empirical evidence from China</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Jeghers et al.</t>
+          <t>Yin et al.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Future Transportation, 4, 1520-1536</t>
+          <t>Transportation Research Part A: Policy and Practice, 211, 105130</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/futuretransp4040073</t>
+          <t>https://doi.org/10.1016/j.tra.2026.105130</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stakeholder perspectives, funding gaps</t>
+          <t>Older adult travel demand</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Interviews with 13 city planners, transportation employees, and state representatives in North Florida find that funding shortfalls and misaligned priorities among stakeholders, not lack of awareness, are the main barriers to equitable transportation for mobility vulnerable populations, and that new technologies are being piloted without yet translating into improved access for those groups.</t>
+          <t>Survey data from 664 Ningbo, China residents show social participation, not physical infrastructure or technology acceptance, is the strongest predictor of older adults' unmet travel demand, while health barriers and functional capacity constrain trips differently for middle aged and 75-plus age groups respectively.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Mobility vulnerable populations: residents below the poverty line, people with disabilities, and older adults with limited transportation options. SWOT framework: strengths, weaknesses, opportunities, and threats used to structure stakeholders' assessment of the transportation system. Smart Cities Collaborative: a multi city initiative piloting technologies like autonomous rideshare intended to reduce transportation disparities.</t>
+          <t>Latent travel demand: unmet mobility need operationalized across four dimensions, health barriers, functional capacity, social participation, and technology acceptance. Active aging: a WHO framework treating older adults as active social participants rather than passive recipients of protection.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Transportation professionals, city planners, agency employees, and state representatives, rather than the mobility vulnerable residents whose needs are being discussed.</t>
+          <t>Older adults in Ningbo, China across three age bands (35-59, 60-74, 75+), studied through survey data rather than direct qualitative accounts.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Equitable access: one participant described a higher minority area of Gainesville as still hurting because state and city funding priorities do not match that community's needs, reflecting a persistent misalignment between resource allocation and who actually needs it.</t>
+          <t>Flexibility for variable need: the study argues age-friendly policy has over-focused on physical infrastructure accommodations while under-investing in social participation opportunities, such as community activity centers and flexible employment, that actually drive older adults' mobility.</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>A moderate fit for the unevenly distributed half, since it documents professionals' own acknowledgment that funding and priorities are misaligned with mobility vulnerable and minority populations. It is thinner on the participation half: the study centers professional perspectives rather than community members, and stakeholders admit new technologies have not yet been communicated to the users they are meant to serve.</t>
+          <t>A thinner fit for this section: the paper documents unmet travel demand among an aging population through quantitative modeling rather than a case of infrastructure built without community participation. It is included as background evidence that equity in older adult mobility may hinge on social participation opportunities rather than only accessible infrastructure.</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>The study interviewed only 13 stakeholders, all transportation professionals, and the authors note responses may be shaped by participants' professional roles or concern about their employers rather than by mobility vulnerable residents' own perspectives.</t>
-        </is>
-      </c>
-      <c r="M24" s="1" t="inlineStr">
-        <is>
-          <t>"Politicians come and go. They have priorities, and they do not always match [the priorities of multiple stakeholders]" (p. 7).</t>
+          <t>Only the abstract, highlights, and introduction of this paywalled article were accessible for this review; the methods, results tables, and discussion sections could not be verified against the source text and should be checked directly before citing specific findings.</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>"age-friendly policy should move beyond physical infrastructure improvement alone" (p. 2, Abstract).</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>This paper documents uneven distribution from the professional side, showing transportation officials themselves recognize that funding and political priorities leave some communities, especially higher minority areas, underserved. It is a weaker source for the participation half, since it centers professionals' self-assessment rather than mobility vulnerable residents' direct accounts of exclusion.</t>
+          <t>This paper is a thin, quantitative complement to the section's argument: it shows that even for older adults, a group facing well documented mobility barriers, unmet travel demand is driven more by social participation opportunities than infrastructure alone. Only the paper's abstract and introduction were available for this review.</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>None described. This is a quantitative theoretical modeling study of latent travel demand using survey and statistical data, not a participatory or co-design process. No focus groups, workshops, interviews, or community consultation appear anywhere in the text.</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Quantification of latent travel demand across age groups with a focus on older adults: a theoretical framework with empirical evidence from China</t>
+          <t>Beyond research delays: science funding disruptions limit community participation in climate and infrastructure planning</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Yin et al.</t>
+          <t>Contreras et al.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2201,573 +2593,693 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Transportation Research Part A: Policy and Practice, 211, 105130</t>
+          <t>npj Urban Sustainability, 6, 71</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.tra.2026.105130</t>
+          <t>https://doi.org/10.1038/s42949-026-00374-5</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Older adult travel demand</t>
+          <t>Federal funding cuts, participation</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Survey data from 664 Ningbo, China residents show social participation, not physical infrastructure or technology acceptance, is the strongest predictor of older adults' unmet travel demand, while health barriers and functional capacity constrain trips differently for middle aged and 75-plus age groups respectively.</t>
+          <t>A four month federal funding suspension halted a community engaged research project meant to center environmental justice organizations in California climate and transportation planning, illustrating how federal science funding disruptions directly reduce vulnerable communities' opportunities to shape infrastructure and climate decisions.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Latent travel demand: unmet mobility need operationalized across four dimensions, health barriers, functional capacity, social participation, and technology acceptance. Active aging: a WHO framework treating older adults as active social participants rather than passive recipients of protection.</t>
+          <t>Epistemic justice: valuing community knowledge as a legitimate form of data on par with quantitative measures. Techno-rational planning: transportation planning dominated by quantitative metrics that can miss lived safety and health concerns communities identify directly. Community-informed data tools: indices like CalEnviroScreen that incorporate community perspectives into official risk assessments.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Older adults in Ningbo, China across three age bands (35-59, 60-74, 75+), studied through survey data rather than direct qualitative accounts.</t>
+          <t>Environmental justice community-based organizations in California, and the researchers partnering with them to incorporate community feedback into climate and transportation risk data tools.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Flexibility for variable need: the study argues age-friendly policy has over-focused on physical infrastructure accommodations while under-investing in social participation opportunities, such as community activity centers and flexible employment, that actually drive older adults' mobility.</t>
+          <t>Equitable access and relational trust: quantitative transportation metrics can certify a route as safe while missing community reported dangers like poor lighting, and defunding the research meant to close that gap removes another avenue for communities' knowledge to count in decisions.</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>A thinner fit for this section: the paper documents unmet travel demand among an aging population through quantitative modeling rather than a case of infrastructure built without community participation. It is included as background evidence that equity in older adult mobility may hinge on social participation opportunities rather than only accessible infrastructure.</t>
+          <t>Directly supports the infrastructure without participation reproduces exclusion half, but through a distinct mechanism: federal funding cuts, not just planning process design, can abruptly cut off the pipeline that lets community knowledge enter climate and transportation decision making, disproportionately affecting the vulnerable communities the project was meant to serve.</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Only the abstract, highlights, and introduction of this paywalled article were accessible for this review; the methods, results tables, and discussion sections could not be verified against the source text and should be checked directly before citing specific findings.</t>
+          <t>As a first person perspective piece about the authors' own disrupted project, it reports process and consequences rather than completed empirical findings on community risk perceptions, since the underlying data collection itself was interrupted.</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>"age-friendly policy should move beyond physical infrastructure improvement alone" (p. 2, Abstract).</t>
+          <t>"the street lacks lighting to illuminate the path at night" (p. 2).</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>This paper is a thin, quantitative complement to the section's argument: it shows that even for older adults, a group facing well documented mobility barriers, unmet travel demand is driven more by social participation opportunities than infrastructure alone. Only the paper's abstract and introduction were available for this review.</t>
+          <t>This paper adds a distinct mechanism to the exclusion claim: federal funding volatility itself can sever the pipeline connecting community knowledge to infrastructure and climate planning, not just weak local process design. It shows concretely how techno-rational transportation metrics miss lived safety concerns communities can name directly, reinforcing why participation must be actively resourced rather than assumed to continue.</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>A planned, multi phase mixed methods project in California pairing semi-structured interviews with environmental justice community based organizations, local planners, policymakers, and engineers on climate and transportation risk perceptions, with a comparative quantitative and spatial analysis testing whether existing risk dashboards match community priorities. Data collection was disrupted four months in when U.S. federal funding was paused, halting the community based organization collaborations before the intended interviews and comparison could be completed.</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>The authors argue, from project design rather than completed data, that community knowledge would have caught risks technical data misses. A route with no recorded pedestrian crashes can still feel unsafe at night due to poor lighting, and residents can report health experiences tied to air pollution that county level regulatory monitoring is too coarse to capture (p. 2).</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>The federal funding pause itself is the central failure. For four months, data collection halted, research staff were reassigned or furloughed, and community based organization partnerships were interrupted, only restarting after legal intervention by universities (p. 2). Even after funding was reinstated about six months later, the team was left restarting on a severely condensed timeline with reduced ability to fulfill the original project's community engaged design (p. 2).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Beyond research delays: science funding disruptions limit community participation in climate and infrastructure planning</t>
+          <t>Towards Environmental Justice in Transportation Decision Making using Structured Public Involvement</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Contreras et al.</t>
+          <t>Bailey et al.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>npj Urban Sustainability, 6, 71</t>
+          <t>Transportation Research Board (TRB) Annual Meeting</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s42949-026-00374-5</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Federal funding cuts, participation</t>
+          <t>Procedural justice, large groups</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>A four month federal funding suspension halted a community engaged research project meant to center environmental justice organizations in California climate and transportation planning, illustrating how federal science funding disruptions directly reduce vulnerable communities' opportunities to shape infrastructure and climate decisions.</t>
+          <t>Reviewing environmental justice and public involvement literature, the authors argue transportation agencies have focused on distributional justice, who bears costs and benefits, while under-theorizing procedural justice, and propose four process metrics plus Structured Public Involvement as a large-group method to make public involvement more inclusive and measurable.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Epistemic justice: valuing community knowledge as a legitimate form of data on par with quantitative measures. Techno-rational planning: transportation planning dominated by quantitative metrics that can miss lived safety and health concerns communities identify directly. Community-informed data tools: indices like CalEnviroScreen that incorporate community perspectives into official risk assessments.</t>
+          <t>Distributional versus procedural justice: the Rawlsian distinction between fair outcomes and fair decision-making processes, the latter chronically under-researched in transportation EJ work. Arnstein Ladder: a scale of public involvement levels used to benchmark how much power a process gives participants. Q-metric: a stakeholder-reported measure of process satisfaction used to evaluate Structured Public Involvement events.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Environmental justice community-based organizations in California, and the researchers partnering with them to incorporate community feedback into climate and transportation risk data tools.</t>
+          <t>Low-income, minority, and other underrepresented transportation stakeholders whose full and fair participation is a stated goal of the 1994 Environmental Justice executive order.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Equitable access and relational trust: quantitative transportation metrics can certify a route as safe while missing community reported dangers like poor lighting, and defunding the research meant to close that gap removes another avenue for communities' knowledge to count in decisions.</t>
+          <t>Relational trust and equitable access: small-group advisory committees are held up as exemplary process even when agencies turn away most attendees to keep the group manageable, compromising the inclusiveness EJ mandates require.</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Directly supports the infrastructure without participation reproduces exclusion half, but through a distinct mechanism: federal funding cuts, not just planning process design, can abruptly cut off the pipeline that lets community knowledge enter climate and transportation decision making, disproportionately affecting the vulnerable communities the project was meant to serve.</t>
+          <t>Directly supports the infrastructure without participation reproduces exclusion half with a documented example: a Virginia DOT advisory committee that shrank from 70 interested citizens to about 30 hand-picked representatives, held up in agency literature as a model process despite excluding most of the public who showed up.</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>As a first person perspective piece about the authors' own disrupted project, it reports process and consequences rather than completed empirical findings on community risk perceptions, since the underlying data collection itself was interrupted.</t>
+          <t>The paper is a conference proceedings submission rather than a peer-reviewed journal article, and its proposed Structured Public Involvement approach is illustrated mainly through the authors' own prior projects rather than independent replication.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>"the street lacks lighting to illuminate the path at night" (p. 2).</t>
+          <t>"asked the citizens to return to their respective interest organizations and identify only one or two persons" (p. 16).</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>This paper adds a distinct mechanism to the exclusion claim: federal funding volatility itself can sever the pipeline connecting community knowledge to infrastructure and climate planning, not just weak local process design. It shows concretely how techno-rational transportation metrics miss lived safety concerns communities can name directly, reinforcing why participation must be actively resourced rather than assumed to continue.</t>
+          <t>This paper's VDOT example is a vivid, documented instance of the exclusion the section describes: an agency-praised process that literally turned away most of the public who showed up to keep the group small. It reinforces that procedural justice, not just distributional outcomes, needs its own metrics, since existing EJ practice has focused far more on who bears costs than on whether decision processes are genuinely inclusive.</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Largely conceptual, drawing on the same authors' prior SPI case study data (AMIS, CAVE) rather than new fieldwork, to propose four process metrics for large group public involvement grounded in Rawlsian procedural and access to justice. The authors also quote, as a cautionary counterexample rather than their own work, a Virginia DOT (VDOT) citizen advisory committee convened via newspaper ads: nearly 70 people attended the first meeting, and VDOT then asked attendees to return to their organizations and nominate only one or two representatives each, paring the group to about 30 members.</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>SPI's anonymous, one person one input, large group format is presented as the alternative that avoids VDOT's problem entirely. Meeting time demands stay the same whether twenty or three hundred people attend, so a sponsor gets more robust, harder to challenge data by including more participants rather than fewer (p. 16).</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>In the VDOT example the authors cite, once nearly 70 attendees were asked to self reduce to one or two representatives per organization, the pared down group of about 30 ended up skewed: more than a third of members still belonged to the same interest group, Friends of Bryan Park, even though this process had been distributed within the transportation field as a model of exemplary group process (p. 16).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Towards Environmental Justice in Transportation Decision Making using Structured Public Involvement</t>
+          <t>The dignity experience of people with disability when using trains and buses in an Australian city</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bailey et al.</t>
+          <t>Chapman et al.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Transportation Research Board (TRB) Annual Meeting</t>
+          <t>Disability &amp; Society, 39(9), 2375-2399</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>https://doi.org/10.1080/09687599.2023.2203307</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Procedural justice, large groups</t>
+          <t>Dignity, disability, public transport</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Reviewing environmental justice and public involvement literature, the authors argue transportation agencies have focused on distributional justice, who bears costs and benefits, while under-theorizing procedural justice, and propose four process metrics plus Structured Public Involvement as a large-group method to make public involvement more inclusive and measurable.</t>
+          <t>Twenty six interviews with people with diverse visible and invisible disabilities in an Australian city find that dignified mobility depends on accessible infrastructure, inclusive information, and respectful staff interactions across an entire journey, and that a single inaccessible link anywhere in that journey makes participants vulnerable to indignity.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Distributional versus procedural justice: the Rawlsian distinction between fair outcomes and fair decision-making processes, the latter chronically under-researched in transportation EJ work. Arnstein Ladder: a scale of public involvement levels used to benchmark how much power a process gives participants. Q-metric: a stakeholder-reported measure of process satisfaction used to evaluate Structured Public Involvement events.</t>
+          <t>Dignified mobility experience: a dynamic interaction between personal preferences, impairment specific needs, infrastructure, staff interactions, and information accessibility across a full journey. Compliance based accessibility: standards like the ADA or Australia's Disability Standards for Accessible Public Transport that rely on voluntary or partial compliance, so meeting a broad standard can still exclude people whose needs it did not anticipate.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Low-income, minority, and other underrepresented transportation stakeholders whose full and fair participation is a stated goal of the 1994 Environmental Justice executive order.</t>
+          <t>People with diverse visible and invisible disabilities in an Australian city, describing their own experiences using buses and trains in their own words.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Relational trust and equitable access: small-group advisory committees are held up as exemplary process even when agencies turn away most attendees to keep the group manageable, compromising the inclusiveness EJ mandates require.</t>
-        </is>
-      </c>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>Directly supports the infrastructure without participation reproduces exclusion half with a documented example: a Virginia DOT citizen advisory committee drew nearly 70 people to its first meeting, and VDOT, feeling the group would be unmanageable, asked them to return to their interest organizations and nominate only one or two persons each. Agency literature holds this up as a model process despite it narrowing the public who actually showed up.</t>
+          <t>Relational trust and flexibility for variable need: compliance based, one-size standards can be met on paper while still excluding people whose particular impairment needs fall outside what the standard anticipated, and staff attitudes frequently produced indignity independent of infrastructure.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Supports the infrastructure without participation reproduces exclusion half by showing that standards developed without embedding diverse disabled people's specific needs in planning can be formally met while still excluding them, and argues policy mandates for including people with diverse impairments in planning are urgently needed.</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>The paper is a conference proceedings submission rather than a peer-reviewed journal article, and its proposed Structured Public Involvement approach is illustrated mainly through the authors' own prior projects rather than independent replication.</t>
+          <t>The study is limited to bus and train systems in one Australian city and does not examine taxis, light rail, ferries, or air travel, or factors like time of day and trip purpose.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>"asked the citizens to return to their respective interest organizations and identify only one or two persons" (p. 16).</t>
+          <t>"being treated like everyone else" (p. 8).</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>This paper's VDOT example is a vivid, documented instance of the exclusion the section describes: an agency-praised process that literally turned away most of the public who showed up to keep the group small. It reinforces that procedural justice, not just distributional outcomes, needs its own metrics, since existing EJ practice has focused far more on who bears costs than on whether decision processes are genuinely inclusive.</t>
+          <t>This paper treats dignity, not just physical access, as the measure of whether transport infrastructure includes disabled people, and traces failures back to compliance based standards built without disabled people's specific needs embedded in planning. It reinforces that infrastructure designed without participation reproduces exclusion, even when it technically satisfies accessibility law.</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>The authors' own method is 26 semi-structured interviews, 25 to 70 minutes, with people with visible and invisible disabilities in an Australian city, analyzed with Framework Analysis. Participants were purposively recruited through a public transport agency's research contact list and newsletter: 75 people expressed interest, 30 were purposively selected, and 26 completed interviews after some attrition. Substantively, participants critique how transit agencies design digital information and communication tools, arguing these are typically built without consulting people with diverse impairments during the design phase.</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Recruiting through an existing public transport agency contact list and newsletter that people had already opted into generated a strong pool, 75 expressed interest for 30 planned interview slots, letting the researchers purposively select for diversity of impairment type and transport use rather than settle for whoever happened to respond (p. 6).</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Participants argued that digital accessibility tools are typically developed without consulting people with diverse impairments, over relying on smartphone technology in ways that widen gaps for marginalised riders who may not have or use smartphones, rather than being informed by lived experience from the design phase onward (p. 20).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>The dignity experience of people with disability when using trains and buses in an Australian city</t>
+          <t>The equity-environmental sustainability nexus in autonomous vehicles: An integrated framework for policy and planning</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Chapman et al.</t>
+          <t>Bahman et al.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Disability &amp; Society, 39(9), 2375-2399</t>
+          <t>Research in Transportation Business &amp; Management</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/09687599.2023.2203307</t>
+          <t>https://doi.org/10.1016/j.rtbm.2026.101689</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dignity, disability, public transport</t>
+          <t>AV equity-sustainability framework</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Twenty six interviews with people with diverse visible and invisible disabilities in an Australian city find that dignified mobility depends on accessible infrastructure, inclusive information, and respectful staff interactions across an entire journey, and that a single inaccessible link anywhere in that journey makes participants vulnerable to indignity.</t>
+          <t>A conceptual literature review argues that AV deployment's environmental sustainability gains and social equity impacts are deeply intertwined rather than separate concerns, and proposes an integrated framework built on proactive planning, meaningful community engagement, and adaptive governance to keep AV deployment from disproportionately burdening marginalized communities.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Dignified mobility experience: a dynamic interaction between personal preferences, impairment specific needs, infrastructure, staff interactions, and information accessibility across a full journey. Compliance based accessibility: standards like the ADA or Australia's Disability Standards for Accessible Public Transport that rely on voluntary or partial compliance, so meeting a broad standard can still exclude people whose needs it did not anticipate.</t>
+          <t>Equity-environmental sustainability nexus: the claim that AV emissions benefits and social equity outcomes are interdependent, so optimizing one without the other risks negative net outcomes. Siloed AV research: the paper's diagnosis that policy, planning, and assessment frameworks currently treat equity and sustainability separately. Social equity: fair distribution of benefits and burdens ensuring equal access regardless of socioeconomic status.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>People with diverse visible and invisible disabilities in an Australian city, describing their own experiences using buses and trains in their own words.</t>
+          <t>The perspective of AV policymakers and planners synthesizing literature; the paper is conceptual rather than centering directly affected riders or communities in its own method.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Relational trust and flexibility for variable need: compliance based, one-size standards can be met on paper while still excluding people whose particular impairment needs fall outside what the standard anticipated, and staff attitudes frequently produced indignity independent of infrastructure.</t>
+          <t>Equitable access: the authors warn that AVs could reduce emissions overall while disproportionately benefiting affluent communities and burdening marginalized ones with more traffic or reduced transit, unless equity is designed in from the start.</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Supports the infrastructure without participation reproduces exclusion half by showing that standards developed without embedding diverse disabled people's specific needs in planning can be formally met while still excluding them, and argues policy mandates for including people with diverse impairments in planning are urgently needed.</t>
+          <t>A moderate, AV specific fit for the section: it names meaningful community engagement as a required component of just AV deployment, directly echoing the participation half of the claim, though at the level of a conceptual framework proposal rather than an empirical case. Most useful for feeding the broader Mobility as Social Service argument given its direct AV focus.</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>The study is limited to bus and train systems in one Australian city and does not examine taxis, light rail, ferries, or air travel, or factors like time of day and trip purpose.</t>
+          <t>Only the abstract, highlights, introduction, and truncated section previews of this paywalled article were accessible; the full literature review, framework details, and discussion could not be read and should be verified directly before citing specific claims from those sections.</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>"being treated like everyone else" (p. 8).</t>
+          <t>"ensuring AVs contribute positively to a future that is both green and fair" (p. 2, Abstract).</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>This paper treats dignity, not just physical access, as the measure of whether transport infrastructure includes disabled people, and traces failures back to compliance based standards built without disabled people's specific needs embedded in planning. It reinforces that infrastructure designed without participation reproduces exclusion, even when it technically satisfies accessibility law.</t>
+          <t>This paper's main relevance is naming meaningful community engagement as a required element of just AV deployment, directly connecting to the section's participation claim within the AV context central to the broader project. Because only the introduction and truncated section previews were accessible, its literature review and framework specifics should be verified from the full text before being cited in detail.</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>None described. This is a conceptual policy framework paper, not an empirical study. It recommends stakeholder engagement and community engagement as abstract steps within a proposed application pathway (Fig. 2), alongside policy adaptation and pilot programs, but names no actual process, participants, location, or outcome.</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>The equity-environmental sustainability nexus in autonomous vehicles: An integrated framework for policy and planning</t>
+          <t>Travelling in the margins: Impacts of transport poverty on travel attitudes and behaviours</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Bahman et al.</t>
+          <t>Nakshi et al.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Research in Transportation Business &amp; Management</t>
+          <t>Transportation Research Part A, 196, 104475</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.rtbm.2026.101689</t>
+          <t>https://doi.org/10.1016/j.tra.2025.104475</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AV equity-sustainability framework</t>
+          <t>Transport poverty, travel attitudes</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>A conceptual literature review argues that AV deployment's environmental sustainability gains and social equity impacts are deeply intertwined rather than separate concerns, and proposes an integrated framework built on proactive planning, meaningful community engagement, and adaptive governance to keep AV deployment from disproportionately burdening marginalized communities.</t>
+          <t>Qualitative interviews in Toronto's Rexdale neighborhood find that repeated experiences of transport poverty, including racism and harassment on transit, shape marginalized residents' travel attitudes and behavior beyond material deprivation alone, and that delayed transit infrastructure investment compounds this by leaving equity-deserving communities without the reliable service needed to sustain positive attitudes toward transit.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Equity-environmental sustainability nexus: the claim that AV emissions benefits and social equity outcomes are interdependent, so optimizing one without the other risks negative net outcomes. Siloed AV research: the paper's diagnosis that policy, planning, and assessment frameworks currently treat equity and sustainability separately. Social equity: fair distribution of benefits and burdens ensuring equal access regardless of socioeconomic status.</t>
+          <t>Transport poverty: the combined effect of social and transportation disadvantages that limit mobility. Perceived behavioural control: a person's sense of their own capacity to choose a travel mode, shaped by past experience of poverty and discrimination. Affective versus cognitive attitude: emotional responses to unsafe or discriminatory transit experiences that drive behavior more than favorable abstract opinions about transit.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>The perspective of AV policymakers and planners synthesizing literature; the paper is conceptual rather than centering directly affected riders or communities in its own method.</t>
+          <t>Low income, racially diverse residents of Rexdale, an inner suburb of Toronto facing stigma and marginalization, describing their own daily travel experiences and adaptations.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Equitable access: the authors warn that AVs could reduce emissions overall while disproportionately benefiting affluent communities and burdening marginalized ones with more traffic or reduced transit, unless equity is designed in from the start.</t>
+          <t>Equitable access and relational trust: repeated racism, sexism, and harassment on transit erode marginalized riders' trust in the system regardless of affordability, while chronically delayed infrastructure projects meant to serve these communities leave that distrust unaddressed.</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>A moderate, AV specific fit for the section: it names meaningful community engagement as a required component of just AV deployment, directly echoing the participation half of the claim, though at the level of a conceptual framework proposal rather than an empirical case. Most useful for feeding the broader Mobility as Social Service argument given its direct AV focus.</t>
+          <t>Supports the unevenly distributed half directly through Rexdale residents' lived experience of transport poverty, and touches the participation half by naming repeated, undelivered infrastructure promises, the delayed Finch West LRT and the closed Line 3 subway serving Scarborough, as a pattern of underinvestment in equity-deserving neighborhoods that compounds distrust.</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Only the abstract, highlights, introduction, and truncated section previews of this paywalled article were accessible; the full literature review, framework details, and discussion could not be read and should be verified directly before citing specific claims from those sections.</t>
+          <t>The qualitative, cross-sectional study covers a single marginalized population in one Toronto neighborhood, and the authors call for testing the framework quantitatively and in other populations and geographies.</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>"ensuring AVs contribute positively to a future that is both green and fair" (p. 2, Abstract).</t>
+          <t>"transportation should be considered as a social policy issue in and beyond Toronto" (p. 15).</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>This paper's main relevance is naming meaningful community engagement as a required element of just AV deployment, directly connecting to the section's participation claim within the AV context central to the broader project. Because only the introduction and truncated section previews were accessible, its literature review and framework specifics should be verified from the full text before being cited in detail.</t>
+          <t>This paper extends the uneven distribution claim into the psychological register, showing that transport poverty shapes not just access but attitudes and trust toward transit, and that repeated delays to infrastructure meant for equity deserving neighborhoods reinforce that distrust. It supports treating transportation as a social policy issue rather than a purely technical one.</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>The authors' own method is four 90 minute focus group discussions with 30 participants plus 20 follow-up semi-structured interviews, 40 to 60 minutes, in Rexdale, Toronto, recruited via the Rexdale Community Hub's North Etobicoke Resident Council mailing list between October and November 2023. Eligibility required financial precarity or chronic health or mobility challenges limiting conventional transit use, and at least five years' Rexdale residency. Sessions asked about experiences and feelings rather than direct attitude questions, and moved from an in person to a Zoom format after recruitment began.</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Recruiting through an established, trusted community hub's resident council mailing list, rather than cold outreach, reached a population meeting narrow precarity and residency criteria. Shifting from planned in person sessions to Zoom, after residents requested it due to caregiving, commuting barriers, health concerns, and work schedules, kept participation open to the same people whose mobility constraints the study was trying to understand (p. 7).</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Recruiting solely through one community hub's mailing list means the sample reflects who was already connected to that hub and skews younger, since younger residents are more likely to be in low income households, so the study cannot speak to how residents outside that network or older residents experience transport poverty (p. 7).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Travelling in the margins: Impacts of transport poverty on travel attitudes and behaviours</t>
+          <t>Transportation barriers and equity: Values and experiences of elected officials</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nakshi et al.</t>
+          <t>Linovski et al.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Transportation Research Part A, 196, 104475</t>
+          <t>Journal of Urban Affairs, 48(5), 1506-1526</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.tra.2025.104475</t>
+          <t>https://doi.org/10.1080/07352166.2025.2507951</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Transport poverty, travel attitudes</t>
+          <t>Elected officials, equity values</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Qualitative interviews in Toronto's Rexdale neighborhood find that repeated experiences of transport poverty, including racism and harassment on transit, shape marginalized residents' travel attitudes and behavior beyond material deprivation alone, and that delayed transit infrastructure investment compounds this by leaving equity-deserving communities without the reliable service needed to sustain positive attitudes toward transit.</t>
+          <t>A national survey and interviews with Canadian local elected officials find they have little direct experience with transportation barriers like unaffordability, disability, or harassment, and while they broadly support procedural equity, they are divided on prioritizing marginalized communities in transportation investment, revealing a disconnect from academic and professional equity discourse.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Transport poverty: the combined effect of social and transportation disadvantages that limit mobility. Perceived behavioural control: a person's sense of their own capacity to choose a travel mode, shaped by past experience of poverty and discrimination. Affective versus cognitive attitude: emotional responses to unsafe or discriminatory transit experiences that drive behavior more than favorable abstract opinions about transit.</t>
+          <t>Procedural equity: fair decision-making process, distinguished from substantive equity, which prioritizes marginalized communities in resource allocation. Technical-rational model: the tendency of transportation research to treat politicians as external to decision-making rather than examining their own values and political context. Fundamental mismatch: a gap between who makes transit decisions and who is most affected by them.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Low income, racially diverse residents of Rexdale, an inner suburb of Toronto facing stigma and marginalization, describing their own daily travel experiences and adaptations.</t>
+          <t>Local elected officials across Canada, surveyed and interviewed directly about their own transportation values and personal experience with transportation barriers.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Equitable access and relational trust: repeated racism, sexism, and harassment on transit erode marginalized riders' trust in the system regardless of affordability, while chronically delayed infrastructure projects meant to serve these communities leave that distrust unaddressed.</t>
+          <t>Equitable access: elected officials who lack lived experience of transportation barriers are less likely to prioritize marginalized communities in investment decisions, even while endorsing fair process in the abstract, meaning decisions get made by people distant from the barriers under discussion.</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Supports the unevenly distributed half directly through Rexdale residents' lived experience of transport poverty, and touches the participation half by naming repeated, undelivered infrastructure promises, the delayed Finch West LRT and the closed Line 3 subway serving Scarborough, as a pattern of underinvestment in equity-deserving neighborhoods that compounds distrust.</t>
+          <t>Directly supports the infrastructure without participation reproduces exclusion half by locating the disconnect at the level of who holds decision-making power in the first place. It shows that the people making transportation investment decisions are demographically and experientially unlike the marginalized communities those decisions most affect.</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>The qualitative, cross-sectional study covers a single marginalized population in one Toronto neighborhood, and the authors call for testing the framework quantitatively and in other populations and geographies.</t>
+          <t>The study surveys elected officials' self-reported values and experience rather than observing actual investment decisions or outcomes, and non-response bias may mean officials less interested in equity were underrepresented.</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>"transportation should be considered as a social policy issue in and beyond Toronto" (p. 15).</t>
+          <t>"a fundamental mismatch between who is making key transit decisions . . . and who is most affected by those decisions" (p. 2, Linovski et al. quoting TransitCenter, 2022, p. 5).</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>This paper extends the uneven distribution claim into the psychological register, showing that transport poverty shapes not just access but attitudes and trust toward transit, and that repeated delays to infrastructure meant for equity deserving neighborhoods reinforce that distrust. It supports treating transportation as a social policy issue rather than a purely technical one.</t>
+          <t>This paper locates the exclusion the section describes at its source, showing that the officials who control transportation investment decisions rarely share the lived experience of transportation barriers themselves, and are divided on whether to prioritize marginalized communities even while endorsing fair process. It reframes participation not just as who gets consulted but as who governs.</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>The authors' own method is a national survey of Canadian local elected officials, developed in consultation with transit authority members, sent to 2,148 mayors and councilors via a university survey center with two email follow ups, yielding 165 responses, an 8.2 percent response rate, plus 38 follow up interviews, 20 minutes to an hour, with survey respondents who opted in, coded using the framework method. The survey and interviews probe how officials themselves learn about and value public consultation with constituents on transportation barriers, rather than directly consulting residents.</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Officials most often learn about constituent transportation barriers from staff reports, 81 percent regularly, and from direct constituent contact like emails, calls, and meetings, 66 percent regularly, with public meetings or open houses used regularly by 60 percent, showing multiple channels rather than one dominant source (p. 12-13). A strong majority, 73 percent, agreed that public consultation is only fair if people from different identities and communities are able to fully participate, signaling broad procedural equity awareness among respondents (p. 13).</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>The survey's own response rate was low, 8.2 percent of 2,148 officials contacted, and the authors flag self-selection: participants who responded may hold stronger than average views on transportation equity, limiting how representative the findings are (p. 9). Constituent associations and advocacy groups, potential channels for organized and marginalized voices, were the least used regular information sources, at 47 percent and 40 percent respectively, well behind staff reports and individual contact (p. 12-13).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Transportation barriers and equity: Values and experiences of elected officials</t>
+          <t>Investigating unfulfilled travel needs for people with travel-limiting conditions using the 2017 National Household Travel Survey (NHTS) data</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Linovski et al.</t>
+          <t>Zhang et al.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Journal of Urban Affairs, 48(5), 1506-1526</t>
+          <t>International Journal of Transportation Science and Technology</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/07352166.2025.2507951</t>
+          <t>https://doi.org/10.1016/j.ijtst.2025.07.009</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Elected officials, equity values</t>
+          <t>Intersectional disability travel needs</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>A national survey and interviews with Canadian local elected officials find they have little direct experience with transportation barriers like unaffordability, disability, or harassment, and while they broadly support procedural equity, they are divided on prioritizing marginalized communities in transportation investment, revealing a disconnect from academic and professional equity discourse.</t>
+          <t>Using 2017 National Household Travel Survey data and a logit model, this study finds that unmet travel needs among people with disabilities vary sharply by race, gender, poverty, and age, and that Hispanic PWD and disabled stay-at-home mothers report suppressed rather than absent travel needs due to systemic barriers and reliance on community trust over formal services.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Procedural equity: fair decision-making process, distinguished from substantive equity, which prioritizes marginalized communities in resource allocation. Technical-rational model: the tendency of transportation research to treat politicians as external to decision-making rather than examining their own values and political context. Fundamental mismatch: a gap between who makes transit decisions and who is most affected by them.</t>
+          <t>Unfulfilled travel need: reduced travel that reflects suppressed aspirations under systemic barriers rather than satisfied mobility. Intersectionality: overlapping identities, disability, race, gender, poverty, that compound and complicate travel disadvantage in ways single-category analysis misses. Suppressed mobility: travel demand that goes unreported because barriers have taught people not to expect service.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Local elected officials across Canada, surveyed and interviewed directly about their own transportation values and personal experience with transportation barriers.</t>
+          <t>People with travel-limiting disabilities in the United States, analyzed through 2017 national survey data disaggregated by race, gender, poverty status, and age.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Equitable access: elected officials who lack lived experience of transportation barriers are less likely to prioritize marginalized communities in investment decisions, even while endorsing fair process in the abstract, meaning decisions get made by people distant from the barriers under discussion.</t>
+          <t>Relational trust and equitable access: Hispanic PWD were found to trust neighbors and community members more than formal service providers, meaning standard demand-responsive planning built around expressed requests can miss needs that trust barriers keep people from voicing.</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Directly supports the infrastructure without participation reproduces exclusion half by locating the disconnect at the level of who holds decision-making power in the first place. It shows that the people making transportation investment decisions are demographically and experientially unlike the marginalized communities those decisions most affect.</t>
+          <t>Supports the unevenly distributed half with quantitative evidence that disability intersects with race, gender, and poverty to produce distinct patterns of suppressed travel need, arguing that transportation equity requires proactive, culturally competent outreach rather than only responding to demand that is already expressed.</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>The study surveys elected officials' self-reported values and experience rather than observing actual investment decisions or outcomes, and non-response bias may mean officials less interested in equity were underrepresented.</t>
-        </is>
-      </c>
-      <c r="M31" s="1" t="inlineStr">
-        <is>
-          <t>"a fundamental mismatch between who is making key transit decisions . . . and who is most affected by those decisions" (p. 2, Linovski et al. quoting TransitCenter, 2022, p. 5).</t>
+          <t>The analysis relies on a single cross-sectional national survey and infers suppressed need indirectly from reduced travel patterns rather than through direct qualitative accounts of why travel was curtailed.</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>"a constrained ability to fulfill their desired travel needs" (p. 14).</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>This paper locates the exclusion the section describes at its source, showing that the officials who control transportation investment decisions rarely share the lived experience of transportation barriers themselves, and are divided on whether to prioritize marginalized communities even while endorsing fair process. It reframes participation not just as who gets consulted but as who governs.</t>
+          <t>This paper adds a methodological caution to the unevenly distributed claim: measured travel frequency can hide suppressed need, especially for groups like Hispanic PWD who trust community networks over formal transportation services after learning not to expect accommodation. It argues equity requires actively uncovering suppressed demand, not just responding to requests already made.</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>None described as the authors' own method. This is a quantitative secondary analysis of 2017 NHTS survey data, not fieldwork with communities. In its recommendations, it cites in passing two other studies' models: Texas Hispanic communities using community health workers as trust building liaisons, and California partnerships with community based organizations that reportedly succeeded at co-designing services (Rodriguez et al., 2024), but gives no detail on either process beyond the citation.</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Investigating unfulfilled travel needs for people with travel-limiting conditions using the 2017 National Household Travel Survey (NHTS) data</t>
+          <t>The promise of Universal Basic Mobility</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Zhang et al.</t>
-        </is>
-      </c>
-      <c r="C32" s="1" t="inlineStr">
-        <is>
-          <t>2025</t>
+          <t>Wander et al.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>International Journal of Transportation Science and Technology</t>
+          <t>Transport Reviews, 46(3), 345-365</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.ijtst.2025.07.009</t>
+          <t>https://doi.org/10.1080/01441647.2025.2574358</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Intersectional disability travel needs</t>
+          <t>Universal Basic Mobility policy</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Using 2017 National Household Travel Survey data and a logit model, this study finds that unmet travel needs among people with disabilities vary sharply by race, gender, poverty, and age, and that Hispanic PWD and disabled stay-at-home mothers report suppressed rather than absent travel needs due to systemic barriers and reliance on community trust over formal services.</t>
+          <t>Reviewing U.S. transportation policy and mobility justice theory, this paper argues Universal Basic Mobility should combine three elements, treating mobility as essential to well-being, targeting resources toward those facing transportation insecurity, and pairing subsidy with adequate service, to avoid repeating past piecemeal, single-mode policies that failed to reduce poverty.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Unfulfilled travel need: reduced travel that reflects suppressed aspirations under systemic barriers rather than satisfied mobility. Intersectionality: overlapping identities, disability, race, gender, poverty, that compound and complicate travel disadvantage in ways single-category analysis misses. Suppressed mobility: travel demand that goes unreported because barriers have taught people not to expect service.</t>
+          <t>Mobility justice: an expanded understanding of mobility as freedom of movement and capability, not just travel speed, central to societal participation and power. Targeted universalism: providing resources unevenly, prioritizing those experiencing transportation insecurity, rather than distributing identical resources to everyone. Transportation insecurity: inability to move safely or in a timely way, concentrated among low income, non-White, and disabled populations.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>People with travel-limiting disabilities in the United States, analyzed through 2017 national survey data disaggregated by race, gender, poverty status, and age.</t>
+          <t>People experiencing transportation insecurity in the U.S., particularly low-income, disabled, immigrant, and non-White residents who lack adequate car access.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Relational trust and equitable access: Hispanic PWD were found to trust neighbors and community members more than formal service providers, meaning standard demand-responsive planning built around expressed requests can miss needs that trust barriers keep people from voicing.</t>
+          <t>Equitable access and flexibility for variable need: past U.S. transportation policy relied almost entirely on supply-side transit investment and one-size-fits-all approaches that do not work in dispersed suburbs where most low-income people of color now live.</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Supports the unevenly distributed half with quantitative evidence that disability intersects with race, gender, and poverty to produce distinct patterns of suppressed travel need, arguing that transportation equity requires proactive, culturally competent outreach rather than only responding to demand that is already expressed.</t>
+          <t>Supports the unevenly distributed half by tracing transportation insecurity to historical disparities in car access along race and income lines, and connects to the participation half by arguing mobility justice requires centering the voices of those experiencing transportation disparities rather than designing policy around a single mode.</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>The analysis relies on a single cross-sectional national survey and infers suppressed need indirectly from reduced travel patterns rather than through direct qualitative accounts of why travel was curtailed.</t>
+          <t>The paper is a conceptual policy review rather than an empirical evaluation of any specific UBM pilot program, so its three-part framework has not yet been tested against outcomes data.</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>"a constrained ability to fulfill their desired travel needs" (p. 14).</t>
+          <t>"mobility resources are unevenly distributed, so the state must target such resources" (p. 14).</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>This paper adds a methodological caution to the unevenly distributed claim: measured travel frequency can hide suppressed need, especially for groups like Hispanic PWD who trust community networks over formal transportation services after learning not to expect accommodation. It argues equity requires actively uncovering suppressed demand, not just responding to requests already made.</t>
+          <t>This paper offers the section a policy level articulation of both claim halves: transportation insecurity is unevenly distributed along race and income lines rooted in decades of car access disparities, and mobility justice requires centering the voices of those most affected rather than designing policy around a single mode. It positions Universal Basic Mobility as a concrete framework for practice.</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>None described. This is a policy review synthesizing survey and evaluation data from several Universal Basic Mobility (mobility wallet) pilot programs in cities like Los Angeles, Oakland, San Joaquin County, and Portland. "Participants" refers to program beneficiaries surveyed about how they used their mobility funds, not community members consulted in designing the programs. No focus groups, workshops, or design process with residents is described.</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>The promise of Universal Basic Mobility</t>
+          <t>Urban planning, the built environment, and subjective well-being: A review of recent research advances</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Wander et al.</t>
+          <t>Mouratidis</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2777,213 +3289,258 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Transport Reviews, 46(3), 345-365</t>
+          <t>Cities, 178, 107404</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/01441647.2025.2574358</t>
+          <t>https://doi.org/10.1016/j.cities.2026.107404</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Universal Basic Mobility policy</t>
+          <t>Built environment, well-being review</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Reviewing U.S. transportation policy and mobility justice theory, this paper argues Universal Basic Mobility should combine three elements, treating mobility as essential to well-being, targeting resources toward those facing transportation insecurity, and pairing subsidy with adequate service, to avoid repeating past piecemeal, single-mode policies that failed to reduce poverty.</t>
+          <t>A narrative review of built environment and subjective well-being research since 2021 finds that public transport investment supports well-being and reduces social exclusion, but can also trigger transit-led gentrification and displacement of economically vulnerable residents, while private car access benefits individual users at the cost of collective health and equity externalities.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Mobility justice: an expanded understanding of mobility as freedom of movement and capability, not just travel speed, central to societal participation and power. Targeted universalism: providing resources unevenly, prioritizing those experiencing transportation insecurity, rather than distributing identical resources to everyone. Transportation insecurity: inability to move safely or in a timely way, concentrated among low income, non-White, and disabled populations.</t>
+          <t>Pathways framework: a conceptual model linking built environment attributes to subjective well-being through life domains like accessibility, work, and social relationships. Transit-led gentrification: new public transport investment attracting more affluent residents and raising housing costs, eroding accessibility benefits meant for existing lower income residents. Mobility-related exclusion: reduced social participation and well-being for those without car access in car-oriented environments.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>People experiencing transportation insecurity in the U.S., particularly low-income, disabled, immigrant, and non-White residents who lack adequate car access.</t>
+          <t>The perspective of researchers synthesizing global built environment and well-being literature; the review spans many population groups rather than centering any one group's direct account.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Equitable access and flexibility for variable need: past U.S. transportation policy relied almost entirely on supply-side transit investment and one-size-fits-all approaches that do not work in dispersed suburbs where most low-income people of color now live.</t>
+          <t>Equitable access: transit investment's accessibility benefits can be lost to displacement for economically vulnerable residents, and the review notes that participatory planning processes representing diverse voices are needed but often absent from how these investments get evaluated.</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Supports the unevenly distributed half by tracing transportation insecurity to historical disparities in car access along race and income lines, and connects to the participation half by arguing mobility justice requires centering the voices of those experiencing transportation disparities rather than designing policy around a single mode.</t>
+          <t>A broad, thinner fit for this section: transportation is one of five review categories in a wide-ranging well-being literature synthesis rather than a dedicated case study. It is most useful for the unevenly distributed half, documenting transit-led displacement and mobility exclusion for non-drivers, and briefly names participatory planning as a needed but underused equity tool.</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>The paper is a conceptual policy review rather than an empirical evaluation of any specific UBM pilot program, so its three-part framework has not yet been tested against outcomes data.</t>
+          <t>As a narrative rather than systematic review, study selection relied on the author's framework and judgment, may exclude relevant studies with a less obvious fit, and draws mainly on English-language research underrepresenting the Global South.</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>"mobility resources are unevenly distributed, so the state must target such resources" (p. 14).</t>
+          <t>"Planning processes could include participatory approaches which enable the representation of diverse voices" (p. 12).</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>This paper offers the section a policy level articulation of both claim halves: transportation insecurity is unevenly distributed along race and income lines rooted in decades of car access disparities, and mobility justice requires centering the voices of those most affected rather than designing policy around a single mode. It positions Universal Basic Mobility as a concrete framework for practice.</t>
+          <t>This review's main relevance is documenting that even beneficial transit investments can produce uneven well-being outcomes through displacement, and that the literature calls for participatory planning to represent diverse voices in built environment decisions. As a broad synthesis spanning far beyond transportation, it functions as supporting context rather than a dedicated case for this section's participation claim.</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>None described. This is a literature synthesis on the built environment and subjective well-being, not the authors' own fieldwork. Participatory processes appear only as an abstract, theoretical concern in a speculative section on generative AI in planning, discussing whose voices AI mediated participation might marginalize, with no concrete process, participants, or outcome named.</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Urban planning, the built environment, and subjective well-being: A review of recent research advances</t>
+          <t>Who faces travel constraints? Analyzing household and individual travel challenges in automobile-dependent central Texas</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mouratidis</t>
+          <t>Situ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Cities, 178, 107404</t>
+          <t>Transport Policy, 174, 103857</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.cities.2026.107404</t>
+          <t>https://doi.org/10.1016/j.tranpol.2025.103857</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Built environment, well-being review</t>
+          <t>Travel constraints, single mothers</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>A narrative review of built environment and subjective well-being research since 2021 finds that public transport investment supports well-being and reduces social exclusion, but can also trigger transit-led gentrification and displacement of economically vulnerable residents, while private car access benefits individual users at the cost of collective health and equity externalities.</t>
+          <t>A multidimensional framework combining household housing and transportation cost burden with individual level health, safety, comfort, accessibility, and time constraints finds that low income households in car dependent central Texas suppress travel demand, and that Black and Hispanic single mother households experience disproportionately severe intra-personal travel constraints.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Pathways framework: a conceptual model linking built environment attributes to subjective well-being through life domains like accessibility, work, and social relationships. Transit-led gentrification: new public transport investment attracting more affluent residents and raising housing costs, eroding accessibility benefits meant for existing lower income residents. Mobility-related exclusion: reduced social participation and well-being for those without car access in car-oriented environments.</t>
+          <t>Housing and Transportation Cost-to-Income Ratio: a household level affordability measure combining housing and travel costs against income. Intra-personal Travel Constraints propensity: an individual level model estimating the probability of facing health, safety, comfort, accessibility, or time barriers to reaching desired destinations. Suppressed travel demand: reduced travel driven by constraint rather than preference.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>The perspective of researchers synthesizing global built environment and well-being literature; the review spans many population groups rather than centering any one group's direct account.</t>
+          <t>Low income, single mother, and racially minoritized households, particularly Black and Hispanic/Latino single mothers, in the car dependent Greater Austin region of central Texas.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Equitable access: transit investment's accessibility benefits can be lost to displacement for economically vulnerable residents, and the review notes that participatory planning processes representing diverse voices are needed but often absent from how these investments get evaluated.</t>
+          <t>Equitable access and flexibility for variable need: car dependent transportation planning assumes a baseline ability to drive and afford a vehicle, which compounds disadvantage for single mother households and those with limited English proficiency, disability, or low income who cannot meet that assumption.</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>A broad, thinner fit for this section: transportation is one of five review categories in a wide-ranging well-being literature synthesis rather than a dedicated case study. It is most useful for the unevenly distributed half, documenting transit-led displacement and mobility exclusion for non-drivers, and briefly names participatory planning as a needed but underused equity tool.</t>
+          <t>Supports the unevenly distributed half with a granular, intersectional account of who bears travel constraints in an automobile dependent region, showing race and gender compound to concentrate the most severe constraints among Black and Hispanic single mothers, and that expanding non-automobile options is necessary to address it.</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>As a narrative rather than systematic review, study selection relied on the author's framework and judgment, may exclude relevant studies with a less obvious fit, and draws mainly on English-language research underrepresenting the Global South.</t>
+          <t>Only the abstract, highlights, and introduction of this paywalled article were accessible; the full methodology, results tables, and discussion could not be read and should be verified directly before citing specific quantitative findings.</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>"Planning processes could include participatory approaches which enable the representation of diverse voices" (p. 12).</t>
+          <t>"single-mother households displayed distinct patterns of constraint" (p. 2, Abstract).</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>This review's main relevance is documenting that even beneficial transit investments can produce uneven well-being outcomes through displacement, and that the literature calls for participatory planning to represent diverse voices in built environment decisions. As a broad synthesis spanning far beyond transportation, it functions as supporting context rather than a dedicated case for this section's participation claim.</t>
+          <t>This paper adds fine-grained, intersectional evidence to the uneven distribution claim, showing that in a car dependent region, travel constraints concentrate most severely among Black and Hispanic single mother households once both affordability and personal barriers are measured together. Only the paper's abstract and introduction were available for this review.</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>None described. This is a quantitative analysis of household and individual travel survey data in automobile dependent central Texas. No focus groups, workshops, interviews, or community consultation process appears anywhere in the text.</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Who faces travel constraints? Analyzing household and individual travel challenges in automobile-dependent central Texas</t>
+          <t>From transportation equity to transportation justice: Within, through, and beyond the state</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Situ</t>
+          <t>Karner et al.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Transport Policy, 174, 103857</t>
+          <t>Journal of Planning Literature</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.tranpol.2025.103857</t>
+          <t>https://doi.org/10.1177/0885412220927691</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Travel constraints, single mothers</t>
+          <t>Transportation equity vs justice</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>A multidimensional framework combining household housing and transportation cost burden with individual level health, safety, comfort, accessibility, and time constraints finds that low income households in car dependent central Texas suppress travel demand, and that Black and Hispanic single mother households experience disproportionately severe intra-personal travel constraints.</t>
+          <t>The authors argue transportation planning should shift from state-centered equity analyses, which mostly measure and reform how benefits and burdens are distributed, toward transportation justice, which demands structural redistribution of political power and resources and treats residents' active participation in decisions as essential, drawing on hybrid case studies where community organizing reshaped state planning outcomes.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Housing and Transportation Cost-to-Income Ratio: a household level affordability measure combining housing and travel costs against income. Intra-personal Travel Constraints propensity: an individual level model estimating the probability of facing health, safety, comfort, accessibility, or time barriers to reaching desired destinations. Suppressed travel demand: reduced travel driven by constraint rather than preference.</t>
+          <t>Transportation equity versus transportation justice: equity as reform of distribution within existing state processes, justice as transformation of the structures and power relations producing inequity. Pro forma public involvement: participation processes solicited to satisfy legal requirements that are unlikely to affect final decisions. Hybrid state and society-centric strategies: community organizations using state planning processes and technical analyses to win real concessions.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Low income, single mother, and racially minoritized households, particularly Black and Hispanic/Latino single mothers, in the car dependent Greater Austin region of central Texas.</t>
+          <t>People of color, low-income people, people with disabilities, older adults, and youth who bear disproportionate transportation burdens, and the community organizations that organize on their behalf.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Equitable access and flexibility for variable need: car dependent transportation planning assumes a baseline ability to drive and afford a vehicle, which compounds disadvantage for single mother households and those with limited English proficiency, disability, or low income who cannot meet that assumption.</t>
+          <t>Relational trust and equitable access: quantitative equity analyses and legally mandated public involvement often produce only incremental reforms while leaving the underlying power positions and well-being of disadvantaged populations unchanged.</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Supports the unevenly distributed half with a granular, intersectional account of who bears travel constraints in an automobile dependent region, showing race and gender compound to concentrate the most severe constraints among Black and Hispanic single mothers, and that expanding non-automobile options is necessary to address it.</t>
+          <t>Directly and centrally supports the infrastructure without participation reproduces exclusion half, and gives concrete counter-examples of genuine participation's effect: a Fresno community-led needs assessment that exposed how little transit access reached identified disadvantaged communities and won a dedicated grant program, and a Bay Area community-developed equity scenario that outperformed the regional agency's preferred plan and won funding concessions.</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Only the abstract, highlights, and introduction of this paywalled article were accessible; the full methodology, results tables, and discussion could not be read and should be verified directly before citing specific quantitative findings.</t>
+          <t>The hybrid case studies described are exceptional, well-organized regional coalitions capable of contending with state agencies on their own terms, so the paper's own examples suggest this level of organizing capacity may not be replicable everywhere.</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>"single-mother households displayed distinct patterns of constraint" (p. 2, Abstract).</t>
+          <t>"it is often pro forma, and its results are unlikely to affect ultimate decisions" (p. 3 of the author manuscript).</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>This paper adds fine-grained, intersectional evidence to the uneven distribution claim, showing that in a car dependent region, travel constraints concentrate most severely among Black and Hispanic single mother households once both affordability and personal barriers are measured together. Only the paper's abstract and introduction were available for this review.</t>
+          <t>This paper offers the section's clearest theoretical statement of the exclusion claim, distinguishing equity as reform from justice as transformation of power, and backs it with two concrete wins, Fresno's community-led needs assessment and the Bay Area's community-authored equity scenario, where organized participation changed what got funded and built. It also cautions that such wins required unusually well-organized coalitions.</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Theoretical and policy synthesis, not new fieldwork, citing many named case examples. Central case: Fresno County Council of Governments' mini-grant program funding advocacy organizations' and schools' public involvement during a regional transportation plan update, plus a community led Health Impact Assessment performed by academic researchers on advocates' behalf to document transportation needs for the county. Also draws on participatory budgeting's four success criteria (Lerner and Secondo 2012) and the Bay Area's Six Wins coalition building its own alternative transportation scenario, plus Arnstein's critique of tokenistic advisory committees.</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Fresno's mini-grant program worked because it let regional equity advocates connect a state level policy campaign to grassroots community organizing, a vertical integration the authors call necessary to represent the most vulnerable people and places (p. 13). The community led Fresno HIA, guided by advocates but performed by academic researchers, let residents identify and communicate their own transportation needs and impacts directly to the county, rather than depending on the agency's own analysis (p. 13-14).</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Citing Arnstein, the authors describe advisory committees as often tokenistic, formed to provide the appearance of representation while input is ignored, with participants risking being coopted for a mere seat at the table (p. 17). More generally, when agencies alone control scope and assumptions in performance analysis, community input can shape parameters only at the margins, positioning communities as data sources for the state rather than holders of power (p. 12-13).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>From transportation equity to transportation justice: Within, through, and beyond the state</t>
+          <t>Enhancing Equity in Public Transportation Using Geographic Information Systems and Spatial Optimization</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Karner et al.</t>
+          <t>Cha et al.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2993,417 +3550,420 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Journal of Planning Literature</t>
+          <t>International Journal of Geospatial and Environmental Research, 7(1), Article 2</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1177/0885412220927691</t>
+          <t>https://dc.uwm.edu/ijger/vol7/iss1/2</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Transportation equity vs justice</t>
+          <t>GIS facility location optimization</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>The authors argue transportation planning should shift from state-centered equity analyses, which mostly measure and reform how benefits and burdens are distributed, toward transportation justice, which demands structural redistribution of political power and resources and treats residents' active participation in decisions as essential, drawing on hybrid case studies where community organizing reshaped state planning outcomes.</t>
+          <t>Using a Maximal Covering Location Problem model applied to Hilliard, Ohio, this study finds that adding roughly 26 to 36 new bus stops chosen through spatial optimization can increase transit access coverage for origin- and destination-based transport disadvantaged areas by around 70 to 78 percent.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Transportation equity versus transportation justice: equity as reform of distribution within existing state processes, justice as transformation of the structures and power relations producing inequity. Pro forma public involvement: participation processes solicited to satisfy legal requirements that are unlikely to affect final decisions. Hybrid state and society-centric strategies: community organizations using state planning processes and technical analyses to win real concessions.</t>
+          <t>Transport disadvantaged: people who need public transportation because they lack access to personal vehicles, often left unserved by transit built around able bodied commuters. Maximal Covering Location Problem: an optimization model that selects facility locations to maximize coverage of a defined demand. Bi-objective model: weighting origin-based and destination-based demand together to find stop locations serving both simultaneously.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>People of color, low-income people, people with disabilities, older adults, and youth who bear disproportionate transportation burdens, and the community organizations that organize on their behalf.</t>
+          <t>Modeled transport disadvantaged populations in Hilliard, Ohio, represented as spatial demand data points rather than through direct community input or interviews.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Relational trust and equitable access: quantitative equity analyses and legally mandated public involvement often produce only incremental reforms while leaving the underlying power positions and well-being of disadvantaged populations unchanged.</t>
+          <t>Relational trust and flexibility for variable need: equity here is defined entirely as a spatial coverage optimization problem solved by planners selecting weights, with no described role for transport disadvantaged residents in defining need or reviewing proposed stops.</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Directly and centrally supports the infrastructure without participation reproduces exclusion half, and gives concrete counter-examples of genuine participation's effect: a Fresno community-led needs assessment that exposed how little transit access reached identified disadvantaged communities and won a dedicated grant program, and a Bay Area community-developed equity scenario that outperformed the regional agency's preferred plan and won funding concessions.</t>
+          <t>A thin fit for this section: the paper is a purely technical GIS optimization study demonstrating how facility placement can mathematically improve coverage for transport disadvantaged areas, but it does not address community participation in decisions at all, illustrating the kind of top-down, technically-defined equity analysis the section's argument pushes against.</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>The hybrid case studies described are exceptional, well-organized regional coalitions capable of contending with state agencies on their own terms, so the paper's own examples suggest this level of organizing capacity may not be replicable everywhere.</t>
-        </is>
-      </c>
-      <c r="M36" s="1" t="inlineStr">
-        <is>
-          <t>"it is often pro forma, and its results are unlikely to affect ultimate decisions" (p. 3 of the author manuscript).</t>
+          <t>The model treats equity solely as spatial coverage and demand estimated from data, with no field validation of whether the transport disadvantaged residents identified would actually use or want the proposed new stops.</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>"some people are excluded from the right of mobility and accessibility" (p. 3).</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>This paper offers the section's clearest theoretical statement of the exclusion claim, distinguishing equity as reform from justice as transformation of power, and backs it with two concrete wins, Fresno's community-led needs assessment and the Bay Area's community-authored equity scenario, where organized participation changed what got funded and built. It also cautions that such wins required unusually well-organized coalitions.</t>
+          <t>This paper exemplifies the technical, top-down equity analysis the section contrasts with participatory approaches: it optimizes bus stop locations mathematically to improve coverage for transport disadvantaged areas without any described role for affected residents in defining need or reviewing outcomes. It is useful as a contrast case showing what equity work looks like when treated as a spatial optimization problem alone.</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>None described. This is a GIS and spatial optimization modeling study of transit equity, not a participatory or community engaged process. No focus groups, workshops, interviews, or community consultation appear anywhere in the text.</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Enhancing Equity in Public Transportation Using Geographic Information Systems and Spatial Optimization</t>
+          <t>Integrating equity in transportation scenario planning: A systematic review</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cha et al.</t>
+          <t>Pan et al.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>International Journal of Geospatial and Environmental Research, 7(1), Article 2</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://dc.uwm.edu/ijger/vol7/iss1/2</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>GIS facility location optimization</t>
+          <t>Scenario planning, equity integration</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Using a Maximal Covering Location Problem model applied to Hilliard, Ohio, this study finds that adding roughly 26 to 36 new bus stops chosen through spatial optimization can increase transit access coverage for origin- and destination-based transport disadvantaged areas by around 70 to 78 percent.</t>
+          <t>A systematic review of academic papers, agency reports, and TRB conference materials finds that equity remains inconsistently integrated into transportation scenario planning, especially for newer scenarios involving emerging technology, and recommends embedding vertical equity analysis and advanced community participation techniques throughout all four phases of the scenario planning process.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Transport disadvantaged: people who need public transportation because they lack access to personal vehicles, often left unserved by transit built around able bodied commuters. Maximal Covering Location Problem: an optimization model that selects facility locations to maximize coverage of a defined demand. Bi-objective model: weighting origin-based and destination-based demand together to find stop locations serving both simultaneously.</t>
+          <t>Vertical equity: allocating costs and benefits based on differing mobility needs, income, and structural inequalities, distinct from horizontal equity's equal treatment of similar groups. Scenario planning: a multi-step process generating and evaluating multiple possible transportation futures rather than one forecast. Community participation as justice-building: training community members in the planning process itself so input can shape long-term plans, not just react to them.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Modeled transport disadvantaged populations in Hilliard, Ohio, represented as spatial demand data points rather than through direct community input or interviews.</t>
+          <t>Underserved and low-income populations, women, and people of color affected by long-range transportation plans, discussed through reviewed studies rather than the paper's own primary data collection.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Relational trust and flexibility for variable need: equity here is defined entirely as a spatial coverage optimization problem solved by planners selecting weights, with no described role for transport disadvantaged residents in defining need or reviewing proposed stops.</t>
+          <t>Equitable access and relational trust: agencies have historically used pro forma public meetings for scenario planning, and the review finds equity considerations are largely absent from newer, technology and economy focused scenarios like electric vehicle policy.</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>A thin fit for this section: the paper is a purely technical GIS optimization study demonstrating how facility placement can mathematically improve coverage for transport disadvantaged areas, but it does not address community participation in decisions at all, illustrating the kind of top-down, technically-defined equity analysis the section's argument pushes against.</t>
+          <t>Directly supports the infrastructure without participation reproduces exclusion half, citing Karner et al.'s point that community participation in scenario planning must go beyond collecting opinions to teaching communities how the process itself works, so their input can actually shape long-term plans rather than being collected and set aside.</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>The model treats equity solely as spatial coverage and demand estimated from data, with no field validation of whether the transport disadvantaged residents identified would actually use or want the proposed new stops.</t>
+          <t>As a review of existing literature and conference materials, the paper's policy recommendations are not yet tested through implementation, and the reviewed practices themselves varied widely in rigor and are unevenly documented.</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>"some people are excluded from the right of mobility and accessibility" (p. 3).</t>
+          <t>"how their participation can affect long-term plans" (p. 21).</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>This paper exemplifies the technical, top-down equity analysis the section contrasts with participatory approaches: it optimizes bus stop locations mathematically to improve coverage for transport disadvantaged areas without any described role for affected residents in defining need or reviewing outcomes. It is useful as a contrast case showing what equity work looks like when treated as a spatial optimization problem alone.</t>
+          <t>This review reinforces the exclusion claim by showing equity, especially community participation, remains inconsistently built into transportation scenario planning, with newer technology-focused scenarios like electric vehicles particularly likely to skip equity analysis. It draws on Karner et al.'s argument that real participation requires teaching communities the planning process itself, not just soliciting opinions.</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Systematic review, not the authors' own fieldwork, synthesizing scenario planning participatory practices across many U.S. state DOT studies, including 16 FHWA workshops in 16 states. Reviewed processes fall into three types: small scale within agency discussions using staff experience (Oregon DOT, Washington State DOT), focus groups or Delphi rounds with cross sector experts spanning public health, real estate, and transportation, and collective public input, such as North Dakota DOT presenting four pre-built scenarios (Rural Renaissance, Cities and Centers, Ghost Towns, Smart and Connected) and gathering public feedback on preferred modes and lifestyles to assess them.</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Cross sector focus groups that pulled in public health, tourism, and epidemiology experts alongside transportation staff surfaced disparities a narrower, transportation only discussion would have missed, such as how catering scenarios to wealthy tourists could worsen social disparities (p. 10). Creating simplified, interactive versions of scenarios for the public helped residents understand and engage with technical tradeoffs rather than just receiving expert conclusions (p. 10).</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Across the reviewed studies, equity was often not explicitly treated as a driving force shaping which scenarios got built at all, apparently because agencies weighed it as less critical than factors like the economy, funding, or climate change (p. 9). Qualitative, participatory evaluation methods were also found less able than quantitative ones to compare policy tradeoffs precisely or determine which policy option was actually best, limiting how much influence participatory input carried in final decisions (p. 10).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Integrating equity in transportation scenario planning: A systematic review</t>
+          <t>Inclusive planning: African policy inventory and South African mobility case study on the exclusion of persons with disabilities</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Pan et al.</t>
+          <t>Vanderschuren et al.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Health Research Policy and Systems, 19, 124</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>https://doi.org/10.1186/s12961-021-00775-1</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Scenario planning, equity integration</t>
+          <t>African disability policy inventory</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>A systematic review of academic papers, agency reports, and TRB conference materials finds that equity remains inconsistently integrated into transportation scenario planning, especially for newer scenarios involving emerging technology, and recommends embedding vertical equity analysis and advanced community participation techniques throughout all four phases of the scenario planning process.</t>
+          <t>A policy inventory across 29 African countries and a South African household survey case study find that most transport policies omit or only superficially address people with disabilities, and that South Africans with disabilities take 27 to 66 percent fewer weekly trips than non-disabled residents, evidence of social isolation produced by policy neglect.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Vertical equity: allocating costs and benefits based on differing mobility needs, income, and structural inequalities, distinct from horizontal equity's equal treatment of similar groups. Scenario planning: a multi-step process generating and evaluating multiple possible transportation futures rather than one forecast. Community participation as justice-building: training community members in the planning process itself so input can shape long-term plans, not just react to them.</t>
+          <t>Universal design: designing environments to be usable by the greatest range of people, contrasted with policies that address disability only superficially. Transport justice framework: an approach linking space and mobility to accessibility that the authors note tends to overlook how differently embodied people interact with infrastructure. Trip frequency as isolation measure: using reduced trip-making as a quantitative proxy for social exclusion.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Underserved and low-income populations, women, and people of color affected by long-range transportation plans, discussed through reviewed studies rather than the paper's own primary data collection.</t>
+          <t>People with disabilities across 29 African countries, with a detailed household survey case study centered on South Africa.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Equitable access and relational trust: agencies have historically used pro forma public meetings for scenario planning, and the review finds equity considerations are largely absent from newer, technology and economy focused scenarios like electric vehicle policy.</t>
+          <t>Equitable access and flexibility for variable need: most reviewed African transport policies omit or superficially address disability, so infrastructure and services are built without accounting for the specific needs of people with different impairments.</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Directly supports the infrastructure without participation reproduces exclusion half, citing Karner et al.'s point that community participation in scenario planning must go beyond collecting opinions to teaching communities how the process itself works, so their input can actually shape long-term plans rather than being collected and set aside.</t>
+          <t>Supports the unevenly distributed half with cross-national policy evidence and South African trip-rate data showing severe disability related mobility gaps. On participation, the paper recommends including community leaders, NGOs, and disability advocacy groups in ongoing infrastructure projects but explicitly acknowledges it did not investigate their actual role, leaving this a recommendation rather than documented evidence.</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>As a review of existing literature and conference materials, the paper's policy recommendations are not yet tested through implementation, and the reviewed practices themselves varied widely in rigor and are unevenly documented.</t>
+          <t>The authors explicitly state they did not investigate the actual role of community leaders, NGOs, and lobby groups in African transport planning, and recommend this as a direction for future research rather than something this study demonstrates.</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>"how their participation can affect long-term plans" (p. 21).</t>
+          <t>"people with disability live less integrated, more isolated lives" (p. 10).</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>This review reinforces the exclusion claim by showing equity, especially community participation, remains inconsistently built into transportation scenario planning, with newer technology-focused scenarios like electric vehicles particularly likely to skip equity analysis. It draws on Karner et al.'s argument that real participation requires teaching communities the planning process itself, not just soliciting opinions.</t>
+          <t>This paper documents severe, quantified disability-related mobility gaps across Africa rooted in policy neglect rather than only infrastructure, supporting the uneven distribution half with concrete trip-rate evidence. Its own honesty about not yet studying community leaders' and disability advocates' actual role in planning marks where the participation half still needs direct empirical grounding.</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Two part study: a 29 country African policy document review that the authors explicitly note made no contact with in country stakeholders, relying only on documents available online, and a secondary analysis of the South African National Household Travel Survey (51,341 households, 157,273 respondents, 2013). The authors also draw on a separate focus group the same research team conducted with users of mobility aids in Tshwane, South Africa, split evenly between crutch and wheelchair users, though this paper gives no further detail on its size, recruitment, or format.</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>The Tshwane focus group let mobility aid users describe concrete, specific barriers, non conducive surfaces, poorly built drop curbs, high speeds, aggressive traffic, that a document review or household survey alone would not surface, and confirmed the survey finding that people with mobility impairment travel far less than other groups (p. 8-9).</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>The authors explicitly acknowledge that the policy document review made no contact with stakeholders in any of the 29 countries studied, relying solely on documents available online and treating document counts as a proxy for a country's actual disability inclusiveness, which they name as the study's main limitation (p. 5). They conclude that even where South Africa's transport policy is the most disability inclusive on paper, no country has yet acted on the UN recommendation that people with disabilities be actively involved in developing transport policies and programmes (p. 9).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Inclusive planning: African policy inventory and South African mobility case study on the exclusion of persons with disabilities</t>
+          <t>Transit Equity in the Face of the COVID-19 Pandemic: A Study of Six Ontario Transit Authorities</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Vanderschuren et al.</t>
+          <t>Sutcliffe et al.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Health Research Policy and Systems, 19, 124</t>
+          <t>SSRN Working Paper</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1186/s12961-021-00775-1</t>
+          <t>https://ssrn.com/abstract=3977617</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>African disability policy inventory</t>
+          <t>Pandemic transit service cuts</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>A policy inventory across 29 African countries and a South African household survey case study find that most transport policies omit or only superficially address people with disabilities, and that South Africans with disabilities take 27 to 66 percent fewer weekly trips than non-disabled residents, evidence of social isolation produced by policy neglect.</t>
+          <t>Interviews with transit officials across six Ontario transit authorities find that pandemic-driven service cuts disproportionately harmed low-income and marginalized riders, and that officials, aware of transit equity concerns, had little practical ability to consult transit users before making rapid cuts, most starkly in Windsor's unilateral shutdown of all transit service.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Universal design: designing environments to be usable by the greatest range of people, contrasted with policies that address disability only superficially. Transport justice framework: an approach linking space and mobility to accessibility that the authors note tends to overlook how differently embodied people interact with infrastructure. Trip frequency as isolation measure: using reduced trip-making as a quantitative proxy for social exclusion.</t>
+          <t>Transit equity: ensuring public transit service changes do not disproportionately burden those who depend on transit most. Emergency decision-making: rapid, top-down authority, such as a mayor's Emergency Measures Bylaw, that bypasses normal consultation processes during a crisis. Transit poverty: a state in which loss of affordable transit forces reliance on far more expensive alternatives like taxis.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>People with disabilities across 29 African countries, with a detailed household survey case study centered on South Africa.</t>
+          <t>Public transit officials and municipal leaders across six Ontario transit authorities, interviewed about their own decision-making during the pandemic's first year.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Equitable access and flexibility for variable need: most reviewed African transport policies omit or superficially address disability, so infrastructure and services are built without accounting for the specific needs of people with different impairments.</t>
+          <t>Equitable access and relational trust: Windsor's mayor unilaterally shut down all transit service for four weeks without consulting transit groups or users, leaving thousands of riders to pay far higher costs or lose access to essential trips entirely.</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Supports the unevenly distributed half with cross-national policy evidence and South African trip-rate data showing severe disability related mobility gaps. On participation, the paper recommends including community leaders, NGOs, and disability advocacy groups in ongoing infrastructure projects but explicitly acknowledges it did not investigate their actual role, leaving this a recommendation rather than documented evidence.</t>
+          <t>Directly supports the infrastructure without participation reproduces exclusion half with a stark example: a mayor's unilateral, unconsulted decision to shut down an entire transit system, using emergency powers, left thousands without transportation and sparked public opposition, even though officials elsewhere in the study expressed awareness of and concern for transit equity.</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>The authors explicitly state they did not investigate the actual role of community leaders, NGOs, and lobby groups in African transport planning, and recommend this as a direction for future research rather than something this study demonstrates.</t>
+          <t>The paper centers transit officials' own accounts of their decision-making rather than interviews with the low-income and marginalized riders who bore the impact of service cuts directly.</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>"people with disability live less integrated, more isolated lives" (p. 10).</t>
+          <t>"Transit groups and users were not consulted prior to this decision being taken" (p. 18).</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>This paper documents severe, quantified disability-related mobility gaps across Africa rooted in policy neglect rather than only infrastructure, supporting the uneven distribution half with concrete trip-rate evidence. Its own honesty about not yet studying community leaders' and disability advocates' actual role in planning marks where the participation half still needs direct empirical grounding.</t>
+          <t>This paper gives the section a sharp, real-time example of the exclusion claim: a mayor's unilateral, unconsulted shutdown of an entire transit system left thousands without transportation, even as officials elsewhere expressed genuine concern for transit equity. It shows that good intentions among decision-makers do not substitute for actual consultation when speed overrides participation.</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>The authors' own method is 11 semi-structured interviews with public transit officials and municipal decision makers across six Ontario transit authorities, asking about pandemic survival first and only probing transit equity directly near the end to see what surfaced unprompted, supplemented by secondary data. Substantively, the paper examines each city's non-binding transit advisory committees, bodies limited to recommendations rather than binding authority, as the main formal channel for transit user input during the pandemic, using Windsor's committee as the central example.</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>In Windsor, sustained pressure from transit users, city councillors, and the transit advisory committee's recommendation that transit be declared essential reversed the mayor's initial suspension of service within about four weeks, showing user and advisory pressure could still force a reversal even without formal decision making power (p. 19).</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Even though a councillor backed motion would have shifted transit authority from the mayor to full council, it failed seven votes to three, leaving the advisory committee's recommendation without lasting effect on who holds power in emergencies (p. 19). Interviewees also said pandemic pressures meant less regular consultation with transit users and advisory groups than normal, so the primary way officials heard from riders became complaints registered with the authority or bus operators rather than proactive engagement (p. 20).</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Transit Equity in the Face of the COVID-19 Pandemic: A Study of Six Ontario Transit Authorities</t>
+          <t>Bike Share Equity for Underrepresented Groups: Analyzing Barriers to System Usage in Baltimore, Maryland</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sutcliffe et al.</t>
+          <t>Grasso et al.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SSRN Working Paper</t>
+          <t>Sustainability, 12(18), 7600</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://ssrn.com/abstract=3977617</t>
+          <t>https://doi.org/10.3390/su12187600</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Pandemic transit service cuts</t>
+          <t>Bike share equity, Baltimore</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Interviews with transit officials across six Ontario transit authorities find that pandemic-driven service cuts disproportionately harmed low-income and marginalized riders, and that officials, aware of transit equity concerns, had little practical ability to consult transit users before making rapid cuts, most starkly in Windsor's unilateral shutdown of all transit service.</t>
+          <t>Survey analysis in Baltimore finds people of color, women, low-income, less-educated, and unemployed residents are underrepresented in Baltimore Bike Share membership, with race and gender specifically associated with distinct barriers, safety concerns for women and difficulty riding with children or cargo for nonwhite residents, that uniform system design does not address.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Transit equity: ensuring public transit service changes do not disproportionately burden those who depend on transit most. Emergency decision-making: rapid, top-down authority, such as a mayor's Emergency Measures Bylaw, that bypasses normal consultation processes during a crisis. Transit poverty: a state in which loss of affordable transit forces reliance on far more expensive alternatives like taxis.</t>
+          <t>Vertical equity: the fair distribution of costs and benefits among groups differing by income or social class, applied here to bike share access. Equity of opportunity versus equity of outcome: whether adequate access has been provided versus whether usage rates actually reflect community demographics. Bike share barriers: safety, personal hygiene, harassment risk, and cargo or child-carrying needs that vary systematically by race and gender.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Public transit officials and municipal leaders across six Ontario transit authorities, interviewed about their own decision-making during the pandemic's first year.</t>
+          <t>Non-member Baltimore residents living within the bike share service area, particularly people of color and women, surveyed directly about their perceived barriers to using the system.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Equitable access and relational trust: Windsor's mayor unilaterally shut down all transit service for four weeks without consulting transit groups or users, leaving thousands of riders to pay far higher costs or lose access to essential trips entirely.</t>
+          <t>Flexibility for variable need and equitable access: a bike share system designed around a narrow user profile does not accommodate riders who need to carry children or cargo, or who reasonably fear harassment or crime, leaving those needs unaddressed by uniform system design.</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Directly supports the infrastructure without participation reproduces exclusion half with a stark example: a mayor's unilateral, unconsulted decision to shut down an entire transit system, using emergency powers, left thousands without transportation and sparked public opposition, even though officials elsewhere in the study expressed awareness of and concern for transit equity.</t>
+          <t>Supports the unevenly distributed half by quantifying who is left out of a specific mobility system and why, and touches the participation half through its policy recommendation for grassroots community outreach, ambassador programs, and community-based design input to reach underrepresented groups rather than relying on system design alone.</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>The paper centers transit officials' own accounts of their decision-making rather than interviews with the low-income and marginalized riders who bore the impact of service cuts directly.</t>
+          <t>The non-user survey has a small sample size that limited the ability to detect effects for some demographic subgroups, and nonresponse bias likely underrepresents residents without regular email access or who are not native English speakers.</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>"Transit groups and users were not consulted prior to this decision being taken" (p. 18).</t>
+          <t>"one of the biggest barriers to biking, across all demographic categories, is concern about personal safety" (p. 12).</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>This paper gives the section a sharp, real-time example of the exclusion claim: a mayor's unilateral, unconsulted shutdown of an entire transit system left thousands without transportation, even as officials elsewhere expressed genuine concern for transit equity. It shows that good intentions among decision-makers do not substitute for actual consultation when speed overrides participation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Bike Share Equity for Underrepresented Groups: Analyzing Barriers to System Usage in Baltimore, Maryland</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Grasso et al.</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Sustainability, 12(18), 7600</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/su12187600</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Bike share equity, Baltimore</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Survey analysis in Baltimore finds people of color, women, low-income, less-educated, and unemployed residents are underrepresented in Baltimore Bike Share membership, with race and gender specifically associated with distinct barriers, safety concerns for women and difficulty riding with children or cargo for nonwhite residents, that uniform system design does not address.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Vertical equity: the fair distribution of costs and benefits among groups differing by income or social class, applied here to bike share access. Equity of opportunity versus equity of outcome: whether adequate access has been provided versus whether usage rates actually reflect community demographics. Bike share barriers: safety, personal hygiene, harassment risk, and cargo or child-carrying needs that vary systematically by race and gender.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Non-member Baltimore residents living within the bike share service area, particularly people of color and women, surveyed directly about their perceived barriers to using the system.</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Flexibility for variable need and equitable access: a bike share system designed around a narrow user profile does not accommodate riders who need to carry children or cargo, or who reasonably fear harassment or crime, leaving those needs unaddressed by uniform system design.</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>Supports the unevenly distributed half by quantifying who is left out of a specific mobility system and why, and touches the participation half through its policy recommendation for grassroots community outreach, ambassador programs, and community-based design input to reach underrepresented groups rather than relying on system design alone.</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>The non-user survey has a small sample size that limited the ability to detect effects for some demographic subgroups, and nonresponse bias likely underrepresents residents without regular email access or who are not native English speakers.</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>"one of the biggest barriers to biking, across all demographic categories, is concern about personal safety" (p. 12).</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
           <t>This paper shows that even a supposedly universal mobility service like bike share reproduces exclusion when designed around a narrow user profile, and that closing the gap requires more than infrastructure alone, community outreach and ambassador programs targeted at underrepresented groups. It supports the uneven distribution half with quantified racial and gender specific barriers.</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>None described as a co-design or consultation process. The authors' own method is a structured, closed-format intercept survey (adapted from NACTO's Bike Share Intercept Survey Toolkit) administered to 109 non-users near eight docking stations, plus a separate member survey (245 usable responses), used to statistically measure barriers to bike share usage by race, gender, income, and other demographics, not to gather open-ended community input into system design.</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
